--- a/workspaces/btc_daily_14days/rsi/rsi_divergence_7_14.xlsx
+++ b/workspaces/btc_daily_14days/rsi/rsi_divergence_7_14.xlsx
@@ -575,46 +575,46 @@
         <v>27</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10.4695246427513</v>
+        <v>10.4356169623634</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>19.97402854768227</v>
+        <v>19.90946525949375</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>23.28942004224237</v>
+        <v>23.2145211647172</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>19.71895455081486</v>
+        <v>19.65608662056149</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4.355548076766738</v>
+        <v>4.341451072601664</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>8.362594067452115</v>
+        <v>8.335975556030441</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>8.279710396951188</v>
+        <v>8.253519869425723</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>7.813635667160092</v>
+        <v>7.789127686872057</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>7.754642813408097</v>
+        <v>7.729936902954506</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>14.3284939901196</v>
+        <v>14.28260024679312</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>10.4139880016692</v>
+        <v>10.3805472812344</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>10.45078021997249</v>
+        <v>10.41753249299295</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>10.03217947764187</v>
+        <v>9.999910703577235</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>14.00087320398433</v>
+        <v>13.95581795294746</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>43</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10.29725935421074</v>
+        <v>10.26331834325153</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>11.01409278093775</v>
+        <v>10.97735940445758</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>10.62182424541849</v>
+        <v>10.58655644517951</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>13.08204415530073</v>
+        <v>13.03952896679019</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>10.21847276585844</v>
+        <v>10.18518490629738</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.861817423083565</v>
+        <v>5.84281680889741</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5.778343443057359</v>
+        <v>5.759780167200113</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.31166518733837</v>
+        <v>5.2948156852054</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>9.912514532530587</v>
+        <v>9.880405752061854</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6.732380593408394</v>
+        <v>6.710234528959589</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>8.860185697123072</v>
+        <v>8.831184096628903</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>4.232717428132169</v>
+        <v>4.218984360709477</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>10.81021231494126</v>
+        <v>10.7748679154542</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>4.064293817019163</v>
+        <v>4.050563861644108</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>63</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.062117235344864</v>
+        <v>3.05101943155519</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3.038732510095919</v>
+        <v>3.027197604729743</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>8.996933252169164</v>
+        <v>8.966055652964357</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10.7180204654724</v>
+        <v>10.68212792796796</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3.826169720229103</v>
+        <v>3.812975655235064</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.714170655054332</v>
+        <v>5.695146137556598</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7.220403344503538</v>
+        <v>7.196609137848895</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.983766259517829</v>
+        <v>1.977390656081162</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8.285541048913515</v>
+        <v>8.257913865553689</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>10.61759000614417</v>
+        <v>10.58209666765541</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.458496634092931</v>
+        <v>2.44973437404677</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>5.676685123308701</v>
+        <v>5.657844155587426</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.111345215024606</v>
+        <v>-1.108499275738971</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>3.916520259203558</v>
+        <v>3.902907900036432</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>72</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.673228346456689</v>
+        <v>1.666389120867393</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.229545788749775</v>
+        <v>4.213628737074814</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>8.004524206067103</v>
+        <v>7.97589270812216</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>6.746990030985586</v>
+        <v>6.7231288471543</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.42907675377846</v>
+        <v>3.416752290066917</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.337065864223256</v>
+        <v>2.328672533046785</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.643836697514594</v>
+        <v>3.631174987905197</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.176509079900548</v>
+        <v>3.165924020925637</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.725013297429989</v>
+        <v>1.718362757850521</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.8736656086242078</v>
+        <v>0.8695198566766393</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.060882602156639</v>
+        <v>2.053145567755195</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>6.274167179672418</v>
+        <v>6.252674257893219</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>4.46131870452605</v>
+        <v>4.44563058281787</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.31975947319021</v>
+        <v>3.307669804796987</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>106</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>8.827316396771153</v>
+        <v>8.795564287308707</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.555940510863429</v>
+        <v>1.548464398748045</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.880967029844498</v>
+        <v>5.858287366024456</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>8.845349734086206</v>
+        <v>8.81315275785385</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>7.364234827535441</v>
+        <v>7.337803856817537</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>7.663966737773833</v>
+        <v>7.636868032640308</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>10.41586159007435</v>
+        <v>10.37932624008689</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>6.169738804441927</v>
+        <v>6.148366826663498</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>8.946981375201993</v>
+        <v>8.915193505888375</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>7.151843554963769</v>
+        <v>7.125922483833378</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>7.894196662712289</v>
+        <v>7.866044431348286</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.146192365564517</v>
+        <v>4.131002440218133</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.833116108125473</v>
+        <v>1.825723636360429</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.137775854975096</v>
+        <v>1.132617393896155</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-5.76446635759315</v>
+        <v>-5.795741530988636</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-4.073002401996618</v>
+        <v>-4.093828194934318</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.7278904264574493</v>
+        <v>-0.7268217859296087</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.467874686710495</v>
+        <v>-2.478209919009046</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.7412911332379224</v>
+        <v>0.7491595499685459</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.973048163529789</v>
+        <v>1.98786296510746</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.953234127525171</v>
+        <v>0.9622214923193724</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.364506625876899</v>
+        <v>2.380382995848919</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.379667441374224</v>
+        <v>-2.390836063975243</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.287853803987659</v>
+        <v>-2.298210220009643</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.491132795610035</v>
+        <v>-2.503197643043947</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.519529841823214</v>
+        <v>-1.526421213098963</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.874677558859631</v>
+        <v>-2.890003012369327</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.1855961709802258</v>
+        <v>0.1892211674810582</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.604549431321253</v>
+        <v>-3.617909358309078</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5.154247326085191</v>
+        <v>5.179094170689147</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.452658725942108</v>
+        <v>1.462881415172959</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.343723728386109</v>
+        <v>-4.359357286502686</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.3097125442791153</v>
+        <v>0.3135581785842305</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.830000050337816</v>
+        <v>2.844473367687229</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4.229632407793503</v>
+        <v>4.250354322936268</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.284568081139618</v>
+        <v>2.29575372620139</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.965446751714019</v>
+        <v>2.980490168753704</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.120688386100213</v>
+        <v>2.132264384028005</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.175758524243129</v>
+        <v>1.182880642013089</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.6962052717547</v>
+        <v>2.709462867895795</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.279019887838629</v>
+        <v>2.290214704954273</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.041791928501347</v>
+        <v>1.048134149739575</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>141</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.534930474116265</v>
+        <v>3.522186223908939</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.051016435620092</v>
+        <v>4.035317588943606</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.1100484382433606</v>
+        <v>0.106465576692564</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.4688804835468758</v>
+        <v>-0.4692963248899602</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.830977302106199</v>
+        <v>1.823071756879948</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.968810218591138</v>
+        <v>4.950664185906675</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>4.88574342080117</v>
+        <v>4.867549867711951</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.288233032268018</v>
+        <v>2.279546503420647</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.649295098867668</v>
+        <v>3.635415557966326</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-4.308126128040946</v>
+        <v>-4.296298296881538</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.671156846021262</v>
+        <v>-1.667466857611771</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-4.481562918755635</v>
+        <v>-4.468615398835368</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.7860348650424172</v>
+        <v>0.7821847505269588</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.808930472040558</v>
+        <v>-1.804623339410419</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.766662363925825</v>
+        <v>-2.771872512207509</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.645995539731608</v>
+        <v>-1.647522494631154</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.58731233375989</v>
+        <v>-2.590969259405981</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.616802798318254</v>
+        <v>-1.619204147437372</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.153333267071119</v>
+        <v>-2.156743525286039</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-3.498909450777433</v>
+        <v>-3.505132461826541</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-5.225397829213016</v>
+        <v>-5.235476196566886</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.40720793951202</v>
+        <v>-2.411706979100948</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-4.111672099085347</v>
+        <v>-4.119472844863161</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.5160746652999393</v>
+        <v>0.5184847585310237</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.5211079330494</v>
+        <v>-3.528300532272937</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.939459559899483</v>
+        <v>-2.945674632424783</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-7.195649811638667</v>
+        <v>-7.211616184929227</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-4.207787530797326</v>
+        <v>-4.216750219622398</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>189</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>5.178519351747823</v>
+        <v>5.159954043303834</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.037845209682906</v>
+        <v>3.024623175063873</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.055674915784735</v>
+        <v>1.049032102979254</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>8.064234926699228</v>
+        <v>8.03579344811255</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.352857077634241</v>
+        <v>4.336391671528631</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>8.358355337692281</v>
+        <v>8.328359541446645</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>8.276545783586464</v>
+        <v>8.246801375535021</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>7.811288649773033</v>
+        <v>7.784164681313477</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>4.573430930848197</v>
+        <v>4.556241072359668</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.132745951239514</v>
+        <v>2.123851414630884</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.8671789732295139</v>
+        <v>0.8632873639811791</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.6898494674280542</v>
+        <v>-0.6881171121433525</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.642496139320038</v>
+        <v>-1.637299010348571</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.2005520417022382</v>
+        <v>0.1992041963320119</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-5.070757907838846</v>
+        <v>-5.079264093645953</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-7.197795438328875</v>
+        <v>-7.209690759936187</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.40709713461618</v>
+        <v>-1.407746118067159</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.815939503146076</v>
+        <v>1.821701812651099</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.021627942873138</v>
+        <v>-1.021785416547061</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-4.336825574969168</v>
+        <v>-4.342886187763817</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.251845616886648</v>
+        <v>1.256897434546204</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.2730129203167877</v>
+        <v>0.2753683381934309</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.88465735524511</v>
+        <v>-2.888493938863569</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-4.764557569965589</v>
+        <v>-4.772582940708212</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-4.969070790410974</v>
+        <v>-4.978185385139916</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.902244016149972</v>
+        <v>-3.909737982064271</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.737854707163933</v>
+        <v>-1.741367091646886</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.0068806207465</v>
+        <v>-2.010407339704393</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>221</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.257692901509486</v>
+        <v>2.2481940460329</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.068812838151601</v>
+        <v>-2.06445690297803</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.418671396428167</v>
+        <v>3.403245387215577</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.191458465687255</v>
+        <v>2.179493540025874</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4.367969377312022</v>
+        <v>4.349690409421193</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.214949611528787</v>
+        <v>4.196706752973171</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.679638128129803</v>
+        <v>3.661917551399732</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>5.025383859899101</v>
+        <v>5.004647003820544</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.153606189323469</v>
+        <v>3.139905372103861</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.84930698479711</v>
+        <v>1.841379928109731</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.891216790489906</v>
+        <v>-2.881497311350557</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.765759445310124</v>
+        <v>-3.752351901847888</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.827238199847862</v>
+        <v>-2.816980116509562</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.7606808804354159</v>
+        <v>-0.7584438201395329</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>204</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.918326385672486</v>
+        <v>1.908419425987006</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.3067527727081156</v>
+        <v>0.3029987336090372</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.87266837983713</v>
+        <v>1.860298007349719</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.022529355581668</v>
+        <v>1.012821601259446</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.43746048694149</v>
+        <v>-3.42979248331077</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.1982900824652916</v>
+        <v>-0.203258048014618</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.263440573152216</v>
+        <v>-1.265813781443171</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.195023348525538</v>
+        <v>2.181205130639867</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.1708422934350153</v>
+        <v>0.165871554182317</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.1903500083997614</v>
+        <v>-0.1920528483733719</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.3974589517837828</v>
+        <v>-0.3953445564956368</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.347296534167064</v>
+        <v>-1.340561731663804</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.67328385398573</v>
+        <v>1.668531549838256</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.41822640203273</v>
+        <v>2.408976994340108</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.280839895013123</v>
+        <v>-3.281360154157646</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.105755683407594</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.53137670276304</v>
+        <v>-2.531558906929405</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.613721995352201</v>
+        <v>-1.613681440467467</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.15214321042447</v>
+        <v>-2.152353671243425</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.039856773888083</v>
+        <v>-2.039946266051103</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-4.094984342331799</v>
+        <v>-4.095464045302286</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.379144439882438</v>
+        <v>-3.379494529052259</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-7.381829881436744</v>
+        <v>-7.38319773183423</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-8.62623495907016</v>
+        <v>-8.628012854262671</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-6.070575884158004</v>
+        <v>-6.071983294022637</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-4.459505570869027</v>
+        <v>-4.460639869045792</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-5.277030730997943</v>
+        <v>-5.278277924414041</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-8.191434321479491</v>
+        <v>-8.193208543906728</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>241</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.6185948748106682</v>
+        <v>0.6131523312172362</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.237792016161777</v>
+        <v>-2.230068856684021</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.6868413519305179</v>
+        <v>0.6771880067733349</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.06190776254622</v>
+        <v>2.045689691553719</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>4.013113103490738</v>
+        <v>3.991725582788419</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.480679522534118</v>
+        <v>3.45946198062078</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>4.228920352197299</v>
+        <v>4.204128126091156</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>5.42576658086427</v>
+        <v>5.396256107394763</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>6.197848693805383</v>
+        <v>6.169624430289097</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>7.426830607441957</v>
+        <v>7.396825805836741</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>7.223452118938589</v>
+        <v>7.19724854035158</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>7.260451288561065</v>
+        <v>7.235126956702743</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>5.59337740537655</v>
+        <v>5.573963400048029</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>5.014410634628874</v>
+        <v>4.996235964318139</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>239</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.447413215607462</v>
+        <v>-1.444542949285591</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.961933673520328</v>
+        <v>1.951800985346715</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.240705134287751</v>
+        <v>3.216078960018201</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>5.881418517941285</v>
+        <v>5.842296767068639</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>5.342997302869115</v>
+        <v>5.309121679698379</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.874748864015785</v>
+        <v>1.855122137604063</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.21120750281969</v>
+        <v>2.188948988938066</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.3482137782759409</v>
+        <v>-0.3585923427804687</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.52409716907156</v>
+        <v>2.505336684354553</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.769552159351079</v>
+        <v>3.748421863608357</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.725050736551168</v>
+        <v>2.712831323637658</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.6605302624691802</v>
+        <v>0.6594853146710662</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.079294081271733</v>
+        <v>1.075886016226924</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.7702756641245116</v>
+        <v>-0.7660168525710915</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>198</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.493438320209918</v>
+        <v>-2.484048740053716</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-3.599961428123727</v>
+        <v>-3.582948333044314</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-8.540284680174864</v>
+        <v>-8.508348333875354</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-7.39993053746641</v>
+        <v>-7.378649451406915</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-5.918149732336445</v>
+        <v>-5.901018899574872</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-6.630808804721909</v>
+        <v>-6.610145841493996</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-6.212593123647309</v>
+        <v>-6.195784270018329</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-5.165688806794989</v>
+        <v>-5.153029181909481</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-7.254482878379683</v>
+        <v>-7.225797354588373</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-5.073820565355469</v>
+        <v>-5.053275358009955</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.751703187615199</v>
+        <v>-2.737856104627504</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-3.735621404253436</v>
+        <v>-3.713148349920161</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.160003887663557</v>
+        <v>-4.136023701131798</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.419649923357902</v>
+        <v>-4.394350397222638</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>229</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.655033295510556</v>
+        <v>1.641023980559339</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.353503350668561</v>
+        <v>1.344563657751529</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.831997089486819</v>
+        <v>1.808326832508484</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.08888777667957</v>
+        <v>1.062996831651773</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.860510229729528</v>
+        <v>1.833603841875764</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.335497614214106</v>
+        <v>-1.341730724944391</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.1081129018566287</v>
+        <v>-0.1247109939171409</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.011638453504304</v>
+        <v>-1.021293778899491</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.551780516150259</v>
+        <v>1.53379291364061</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.766244635569031</v>
+        <v>3.737112442697352</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>5.752813342848704</v>
+        <v>5.716842119655141</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>5.349118684657114</v>
+        <v>5.321004789101877</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.174055717119138</v>
+        <v>3.159196338944234</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.548151222590143</v>
+        <v>2.537412648077584</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>208</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.833484756712998</v>
+        <v>1.812209145011707</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.7396273177896191</v>
+        <v>-0.7362105145151361</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.134496024386209</v>
+        <v>-1.145280773557488</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.9188340312981111</v>
+        <v>0.8833628042549293</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.5811256453124187</v>
+        <v>-0.6005488806076968</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.081700907787756</v>
+        <v>3.038835017880338</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.521676436477328</v>
+        <v>2.477848622629409</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.795218539376528</v>
+        <v>-1.802901522626172</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.034565233591913</v>
+        <v>1.012994512664278</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.631131391711385</v>
+        <v>1.606186049336209</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.02426556960114823</v>
+        <v>-0.03088433200154839</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.005074041727333167</v>
+        <v>0.006283134416385394</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.4200173731067522</v>
+        <v>-0.4134532320714683</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.6547277073459057</v>
+        <v>-0.6453216481938284</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>178</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.8080450617829698</v>
+        <v>-0.8143150376756054</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.198358853342619</v>
+        <v>3.166717580769159</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.241692393937072</v>
+        <v>2.194702742876444</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-7.740414024017191</v>
+        <v>-7.711329977188434</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-4.895976004230782</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-8.543191054182721</v>
+        <v>-8.497261471161629</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-6.383141608722646</v>
+        <v>-6.363878820693415</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.352046735092323</v>
+        <v>-2.35800034083757</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-5.233648796880857</v>
+        <v>-5.206648769880864</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.011682710367587</v>
+        <v>-1.023255682638322</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.223193650271753</v>
+        <v>-1.221639843149802</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.6317930701419101</v>
+        <v>-0.6241244575075413</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.338599493476401</v>
+        <v>2.322474695495309</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.023677388067568</v>
+        <v>2.012413874710226</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>164</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-3.712950515331897</v>
+        <v>-3.688955194419485</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.1632807497526017</v>
+        <v>0.1509498209503803</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2315879568440238</v>
+        <v>-0.273246500094821</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.320847019358439</v>
+        <v>-1.351174438844986</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-3.688536527113541</v>
+        <v>-3.68453730696141</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-4.00085068695882</v>
+        <v>-3.98452053800451</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-5.917774343011068</v>
+        <v>-5.894401174235277</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-3.33385412393865</v>
+        <v>-3.33146005974708</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.2728890223370115</v>
+        <v>0.249934539552612</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.414537436359574</v>
+        <v>-2.415687336476367</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.403091669987205</v>
+        <v>-1.398710622989455</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.924361291335195</v>
+        <v>2.894976002433133</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.888826749229985</v>
+        <v>1.869952311427447</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>6.458012099170951</v>
+        <v>6.390325631355886</v>
       </c>
     </row>
     <row r="27">
@@ -1664,49 +1664,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.621669593459131</v>
+        <v>3.596058828646008</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>7.046067203516415</v>
+        <v>7.001821325296682</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.5430461073967265</v>
+        <v>-0.5655306233338635</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-2.571066356084138</v>
+        <v>-2.581919223623345</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.4876347310019185</v>
+        <v>0.4674476185981291</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>6.540472352170859</v>
+        <v>6.493133601397652</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.590572710311392</v>
+        <v>3.552886147899208</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.411100653020959</v>
+        <v>2.381527814576067</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.524848556727676</v>
+        <v>4.488619129246196</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.958560770760208</v>
+        <v>2.928936396364257</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.925156572302107</v>
+        <v>4.893592675692226</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.962987067768054</v>
+        <v>4.934955988081043</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.545617328992975</v>
+        <v>4.520351329064098</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.297939709467386</v>
+        <v>2.28109975648848</v>
       </c>
     </row>
     <row r="28">
@@ -1716,49 +1716,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.412811679789982</v>
+        <v>1.389743761399664</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-4.105011933174254</v>
+        <v>-4.099465927250201</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-6.843630639770822</v>
+        <v>-6.83688877631937</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-2.807127507163365</v>
+        <v>-2.82123515973263</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-3.345548722235492</v>
+        <v>-3.350782765326308</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.0768932154801476</v>
+        <v>0.04898987317476866</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-7.433222009871123</v>
+        <v>-7.41905430461199</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-5.550102823449322</v>
+        <v>-5.543251200238231</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-7.181483498804397</v>
+        <v>-7.161001038825844</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-8.825412017210411</v>
+        <v>-8.794973894645779</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-8.255713154925289</v>
+        <v>-8.219411452805879</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-6.657422271748302</v>
+        <v>-6.625710877416545</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-6.301464545595174</v>
+        <v>-6.270572962299319</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-4.463741499025808</v>
+        <v>-4.446048480416778</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>96</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-4.576771653543304</v>
+        <v>-4.556057268360199</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.144988066825803</v>
+        <v>2.053601073370835</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.875119360229142</v>
+        <v>4.689995422058949</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.244627507163322</v>
+        <v>-1.325831378490442</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.341951277764508</v>
+        <v>1.238031210921463</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.5977265488135046</v>
+        <v>0.4832752189151464</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.5129928315412258</v>
+        <v>0.4236076484191358</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.05830007025037531</v>
+        <v>-0.01664375469339774</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.097993591166947</v>
+        <v>2.008441457398249</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.2000974640397857</v>
+        <v>0.1526045923925921</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>4.196238477835152</v>
+        <v>4.10927731693036</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4.236194223184519</v>
+        <v>4.159938188855904</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>2.757105104417853</v>
+        <v>2.710726250299111</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>5.149841086180174</v>
+        <v>5.043780915908734</v>
       </c>
     </row>
     <row r="30">
@@ -1820,49 +1820,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.126349712615038</v>
+        <v>-3.126109629175787</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-3.472100540769169</v>
+        <v>-3.478662821442974</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-7.664437601796102</v>
+        <v>-7.669559381834162</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-5.002538899568385</v>
+        <v>-5.01705060967624</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.4776689754000358</v>
+        <v>-0.5172827428819957</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.446049822494551</v>
+        <v>-1.489398221254241</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.53078353976678</v>
+        <v>-1.561487544057513</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.984916910547618</v>
+        <v>-2.008340037728352</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.062223394695174</v>
+        <v>3.010262681708419</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.3438022508858367</v>
+        <v>-0.3639312530026686</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.298953795451098</v>
+        <v>3.261402741711592</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>3.33922121367371</v>
+        <v>3.30706807190569</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>4.912756197813749</v>
+        <v>4.874187788760608</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>5.177605656054908</v>
+        <v>5.123909121036938</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>65</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1857460125176615</v>
+        <v>-0.2619546336179113</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-6.412704240866539</v>
+        <v>-6.367455372088237</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-3.730649870540056</v>
+        <v>-3.859251918646741</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-8.215781353317169</v>
+        <v>-8.202286076664038</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.061894876081674</v>
+        <v>-1.240508831785384</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.7644529383659631</v>
+        <v>-0.9946664812730006</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.8491866556382917</v>
+        <v>-1.017480693901362</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.803432277981003</v>
+        <v>1.589036000592557</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.876564548029769</v>
+        <v>-2.974731875614331</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>2.491805181905619</v>
+        <v>2.318612361653983</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3.880960253699357</v>
+        <v>3.681757066448363</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.7688706741338436</v>
+        <v>0.679057784320932</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>3.487077601650512</v>
+        <v>3.335726250299153</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>2.232433029560852</v>
+        <v>2.046986044113865</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>41</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.604122655399784</v>
+        <v>3.346521704257817</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>9.309622213167231</v>
+        <v>8.85946670490074</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-5.719392834892773</v>
+        <v>-5.872747247278319</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-3.150115312041372</v>
+        <v>-3.297008162107232</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-8.566585307601343</v>
+        <v>-8.620431660264828</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-5.830118979641817</v>
+        <v>-6.054119806721751</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-8.353877087157962</v>
+        <v>-8.39006183614778</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-3.907959231374825</v>
+        <v>-4.083221601759085</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-11.36786008899865</v>
+        <v>-11.25092177241615</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-14.78014952298081</v>
+        <v>-14.49695754740862</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-15.05047967204761</v>
+        <v>-14.75611465943193</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-17.68518591528863</v>
+        <v>-17.21962889485355</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-13.0580150519788</v>
+        <v>-12.76183472531064</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-25.3142447927267</v>
+        <v>-24.70723534425387</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>37</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.560615733844081</v>
+        <v>1.214842107869103</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-8.159065987228281</v>
+        <v>-8.142870501234157</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-11.25663739652758</v>
+        <v>-11.26959378532288</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-5.72097885851467</v>
+        <v>-5.855401392266081</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-11.66480547899225</v>
+        <v>-11.61783856960923</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-22.1781743520874</v>
+        <v>-21.8283518546139</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-19.56020536665697</v>
+        <v>-19.12130769621569</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-17.38555774522906</v>
+        <v>-17.08119933276259</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-9.320366455027155</v>
+        <v>-9.21339491948423</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-7.51874745722418</v>
+        <v>-7.362502233742553</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-10.57200624487776</v>
+        <v>-10.27256887647491</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-5.12157660276204</v>
+        <v>-4.892667787404619</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-11.13492430680003</v>
+        <v>-10.71832780375492</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-8.023755078029147</v>
+        <v>-7.765903768775949</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>28</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-6.064866891638523</v>
+        <v>-6.224305667148741</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.037845209682942</v>
+        <v>2.400090107642114</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.9284520683422528</v>
+        <v>-1.56620717038308</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.7981989357347743</v>
+        <v>-1.329661520768767</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-1.336620150806944</v>
+        <v>-1.868082735840936</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1.039178213091262</v>
+        <v>-1.676933315132089</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2.447516641065029</v>
+        <v>1.916054056031015</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-1.510076272222371</v>
+        <v>-1.915171556835702</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-5.201350837753715</v>
+        <v>-5.256783210259208</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>1.214832169908355</v>
+        <v>0.9721255051833424</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-2.759883777582942</v>
+        <v>-2.693746211445372</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-6.746799216834795</v>
+        <v>-6.244019138756016</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.4278828810810751</v>
+        <v>0.478583393156228</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-6.799031300661312</v>
+        <v>-6.414552417424602</v>
       </c>
     </row>
   </sheetData>
@@ -2213,10 +2213,8 @@
           <t>X &gt; -34.88</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4080~4093</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4080</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.1357544697335555</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -32.43</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4053~4066</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4053</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.2061781136187264</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -29.99</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4010~4023</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4010</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.3184445344779405</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -27.54</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3947~3960</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3947</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.3722261989978506</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -25.1</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3875~3888</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3875</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.4101049868766395</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -22.65</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3769~3782</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3769</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.6690068024944793</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -20.21</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3663~3675</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3663</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.5206492045637177</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -17.76</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3529~3540</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3529</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.403042839983982</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -15.32</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3388~3399</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3388</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.5664009562794021</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -12.87</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3206~3216</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3206</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.4411995142398197</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -10.43</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3017~3027</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3017</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.7920838438307172</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -7.984</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2824~2833</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2824</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.4990860434715358</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; -5.539</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2603~2612</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2603</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.7323357168409075</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; -3.094</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2399~2408</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2399</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.9568934697116447</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; -0.6492</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2146~2154</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2146</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.6828533619927128</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 1.796</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1905~1913</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1905</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.846809987747875</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 4.241</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1666~1674</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1666</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.7610607813808201</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 6.686</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1468~1476</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1468</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.5286686725135041</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 9.131</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1239~1247</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1239</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.9296853129926603</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 11.58</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1031~1039</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1031</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-1.482851217226333</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 14.02</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>853~861</t>
-        </is>
+      <c r="B26" t="n">
+        <v>853</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-1.622358180837146</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 16.47</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>689~697</t>
-        </is>
+      <c r="B27" t="n">
+        <v>689</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-1.130454102132497</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 18.91</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>551~558</t>
-        </is>
+      <c r="B28" t="n">
+        <v>551</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-2.314226850675929</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 21.36</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>424~430</t>
-        </is>
+      <c r="B29" t="n">
+        <v>424</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-3.423670878349512</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 23.8</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>328~334</t>
-        </is>
+      <c r="B30" t="n">
+        <v>328</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-3.092240715419557</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 26.25</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>250~255</t>
-        </is>
+      <c r="B31" t="n">
+        <v>250</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-3.08167361432762</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 28.69</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>185~190</t>
-        </is>
+      <c r="B32" t="n">
+        <v>185</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-4.07238568863103</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 31.14</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>144~149</t>
-        </is>
+      <c r="B33" t="n">
+        <v>144</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-6.184713487995211</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 33.58</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>107~112</t>
-        </is>
+      <c r="B34" t="n">
+        <v>107</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-8.743438320209975</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 36.02</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>79~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>79</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-9.636295463067121</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -34.88</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>7.03037120359955</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -32.43</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>111~111</t>
-        </is>
+      <c r="B7" t="n">
+        <v>111</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>7.866922040150392</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -29.99</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>154~154</t>
-        </is>
+      <c r="B8" t="n">
+        <v>154</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>8.545522718751059</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -27.54</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>217~217</t>
-        </is>
+      <c r="B9" t="n">
+        <v>217</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>6.953566288084957</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -25.1</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>289~289</t>
-        </is>
+      <c r="B10" t="n">
+        <v>289</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>5.638049569063384</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -22.65</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>395~395</t>
-        </is>
+      <c r="B11" t="n">
+        <v>395</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>6.493903451941925</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -20.21</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>501~502</t>
-        </is>
+      <c r="B12" t="n">
+        <v>501</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>3.881063671821906</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -17.76</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>635~637</t>
-        </is>
+      <c r="B13" t="n">
+        <v>635</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>2.294630753573387</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -15.32</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>776~778</t>
-        </is>
+      <c r="B14" t="n">
+        <v>776</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>2.51941515022704</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -12.87</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>958~961</t>
-        </is>
+      <c r="B15" t="n">
+        <v>958</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>1.512805176147992</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -10.43</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1147~1150</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1147</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>2.115257331963939</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -7.984</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1340~1344</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1340</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>1.077990251218594</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; -5.539</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1561~1565</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1561</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>1.244580849119103</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; -3.094</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1765~1769</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1765</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1.322276773063052</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; -0.6492</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2018~2023</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2018</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.7443273743031185</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 1.796</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2259~2264</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2259</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.7309433052317189</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 4.241</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2498~2503</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2498</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.5229420233777233</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 6.686</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2696~2701</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2696</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.3018226942291236</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 9.131</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2925~2930</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2925</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.4075855705750087</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 11.58</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3133~3138</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3133</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0.5021002393821163</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 14.02</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3311~3316</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3311</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>0.4317727774981037</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 16.47</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3475~3480</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3475</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.2364467372612822</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 18.91</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3613~3619</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3613</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.3664677311854376</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 21.36</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3740~3747</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3740</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.4022115330059322</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 23.8</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3836~3843</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3836</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.277834123193621</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 26.25</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3914~3922</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3914</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.2092643824927194</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 28.69</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3979~3987</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3979</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.2028245340664228</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 31.14</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4020~4028</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4020</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.2374454930968781</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 33.58</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4057~4065</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4057</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.2494891090643137</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 36.02</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4085~4093</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4085</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.206292928263025</v>

--- a/workspaces/btc_daily_14days/rsi/rsi_divergence_7_14.xlsx
+++ b/workspaces/btc_daily_14days/rsi/rsi_divergence_7_14.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that RSI Divergence-7-14 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that RSI Divergence-7-14 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>27</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10.4356169623634</v>
+        <v>10.44810671016702</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>19.90946525949375</v>
+        <v>19.9223508716062</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>23.2145211647172</v>
+        <v>23.22750793653673</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>19.65608662056149</v>
+        <v>19.66904492707636</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4.341451072601664</v>
+        <v>4.354534570248738</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>8.335975556030441</v>
+        <v>8.34899616380131</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>8.253519869425723</v>
+        <v>8.266566496859163</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>7.789127686872057</v>
+        <v>7.802291482191393</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>7.729936902954506</v>
+        <v>7.743121326129184</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>14.28260024679312</v>
+        <v>14.29599532994099</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>10.3805472812344</v>
+        <v>10.39399629534613</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>10.41753249299295</v>
+        <v>10.43097924405583</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>9.999910703577235</v>
+        <v>10.01346394241637</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>13.95581795294746</v>
+        <v>13.9453883172493</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>43</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10.26331834325153</v>
+        <v>10.27580753325392</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>10.97735940445758</v>
+        <v>10.99023820996416</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>10.58655644517951</v>
+        <v>10.59953452501713</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>13.03952896679019</v>
+        <v>13.05248301703464</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>10.18518490629738</v>
+        <v>10.19827123342554</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.84281680889741</v>
+        <v>5.855835862020385</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5.759780167200113</v>
+        <v>5.772825430557461</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.2948156852054</v>
+        <v>5.30797830062069</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>9.880405752061854</v>
+        <v>9.893590634687172</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6.710234528959589</v>
+        <v>6.72362761706421</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>8.831184096628903</v>
+        <v>8.84463271114646</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>4.218984360709477</v>
+        <v>4.232430267045231</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>10.7748679154542</v>
+        <v>10.78842116427941</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>4.050563861644108</v>
+        <v>4.040134225948073</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>63</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.05101943155519</v>
+        <v>3.063501968749819</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3.027197604729743</v>
+        <v>3.040069706560899</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>8.966055652964357</v>
+        <v>8.979032016647544</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10.68212792796796</v>
+        <v>10.69508001911033</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3.812975655235064</v>
+        <v>3.826057811101471</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.695146137556598</v>
+        <v>5.708164555525052</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7.196609137848895</v>
+        <v>7.209654550793168</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.977390656081162</v>
+        <v>1.990551555803954</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8.257913865553689</v>
+        <v>8.271097940571636</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>10.58209666765541</v>
+        <v>10.59549047202124</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.44973437404677</v>
+        <v>2.463181573574857</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>5.657844155587426</v>
+        <v>5.671290089594429</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.108499275738971</v>
+        <v>-1.094946845920866</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>3.902907900036432</v>
+        <v>3.892478264336837</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>72</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.666389120867393</v>
+        <v>1.67886918308897</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.213628737074814</v>
+        <v>4.226500570004212</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>7.97589270812216</v>
+        <v>7.988867514257599</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>6.7231288471543</v>
+        <v>6.736077616938665</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.416752290066917</v>
+        <v>3.429833295463126</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.328672533046785</v>
+        <v>2.341688415784049</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.631174987905197</v>
+        <v>3.644218132499212</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.165924020925637</v>
+        <v>3.179084721789671</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.718362757850521</v>
+        <v>1.731544243956058</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.8695198566766393</v>
+        <v>0.8829107811309314</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.053145567755195</v>
+        <v>2.06659235498514</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>6.252674257893219</v>
+        <v>6.266120075888217</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>4.44563058281787</v>
+        <v>4.459183254436958</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.307669804796987</v>
+        <v>3.2972401691001</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>106</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>8.795564287308707</v>
+        <v>8.320819318972838</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.548464398748045</v>
+        <v>1.561332384116483</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.858287366024456</v>
+        <v>5.8712593183987</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>8.81315275785385</v>
+        <v>8.826101793727759</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>7.337803856817537</v>
+        <v>7.350886042902204</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>7.636868032640308</v>
+        <v>7.649885689486077</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>10.37932624008689</v>
+        <v>10.39237169908509</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>6.148366826663498</v>
+        <v>6.161527888671259</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>8.915193505888375</v>
+        <v>8.928376739595137</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>7.125922483833378</v>
+        <v>7.139314513727747</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>7.866044431348286</v>
+        <v>7.879491971573415</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.131002440218133</v>
+        <v>4.144447695784393</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.825723636360429</v>
+        <v>1.839275979465391</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.132617393896155</v>
+        <v>1.122187758197143</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>106</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-5.795741530988636</v>
+        <v>-5.78461884129355</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-4.093828194934318</v>
+        <v>-4.584260800225849</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.7268217859296087</v>
+        <v>-0.7138569416893219</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.478209919009046</v>
+        <v>-2.46527062037611</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.7491595499685459</v>
+        <v>0.7622359651969219</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.98786296510746</v>
+        <v>2.000876067745381</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.9622214923193724</v>
+        <v>0.9752611583138133</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.380382995848919</v>
+        <v>2.393541379409363</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.390836063975243</v>
+        <v>-2.377657739578893</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.298210220009643</v>
+        <v>-2.284821626943035</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.503197643043947</v>
+        <v>-2.489752880063861</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.526421213098963</v>
+        <v>-1.512977169953267</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.890003012369327</v>
+        <v>-2.876451225764853</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.1892211674810582</v>
+        <v>0.1787915317837587</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>134</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.617909358309078</v>
+        <v>-3.606264728070578</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5.179094170689147</v>
+        <v>5.193636254728432</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.462881415172959</v>
+        <v>1.077810852616572</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.359357286502686</v>
+        <v>-4.346422283798823</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.3135581785842305</v>
+        <v>0.3266320086798871</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.844473367687229</v>
+        <v>2.85748510008743</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4.250354322936268</v>
+        <v>4.263394082936294</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.29575372620139</v>
+        <v>2.308910615375758</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.980490168753704</v>
+        <v>2.993669211911119</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.132264384028005</v>
+        <v>2.14565323952035</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.182880642013089</v>
+        <v>1.196325409522743</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.709462867895795</v>
+        <v>2.722907018552334</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.290214704954273</v>
+        <v>2.303766604535539</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.048134149739575</v>
+        <v>1.037704514040911</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>141</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.522186223908939</v>
+        <v>3.535867081785184</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.035317588943606</v>
+        <v>4.049654566399219</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.106465576692564</v>
+        <v>0.1197984227963076</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.4692963248899602</v>
+        <v>-0.4563617605967139</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.823071756879948</v>
+        <v>1.83614382904458</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.950664185906675</v>
+        <v>4.963675041248237</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>4.867549867711951</v>
+        <v>4.880588085523343</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.279546503420647</v>
+        <v>2.292701535786115</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.635415557966326</v>
+        <v>3.648593408215532</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-4.296298296881538</v>
+        <v>-4.282912924366023</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.667466857611771</v>
+        <v>-1.654023816133126</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-4.468615398835368</v>
+        <v>-4.455173116044584</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.7821847505269588</v>
+        <v>0.795736200026262</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.804623339410419</v>
+        <v>-1.815052975108415</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>182</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.771872512207509</v>
+        <v>-2.760038142543159</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.647522494631154</v>
+        <v>-1.634814295983588</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.590969259405981</v>
+        <v>-2.578444968820548</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.619204147437372</v>
+        <v>-1.901095567323239</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.156743525286039</v>
+        <v>-2.143678614541329</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-3.505132461826541</v>
+        <v>-3.492130974935641</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-5.235476196566886</v>
+        <v>-5.222447296850397</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.411706979100948</v>
+        <v>-2.398557142138699</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-4.119472844863161</v>
+        <v>-4.106300662664204</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.5184847585310237</v>
+        <v>0.5318698797174477</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.528300532272937</v>
+        <v>-3.514859498933255</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.945674632424783</v>
+        <v>-2.932233134623814</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-7.211616184929227</v>
+        <v>-7.198065964515969</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-4.216750219622398</v>
+        <v>-4.227179855320429</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>189</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>5.159954043303834</v>
+        <v>5.174332863823786</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.024623175063873</v>
+        <v>3.038855188101991</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.049032102979254</v>
+        <v>1.062703515677505</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>8.03579344811255</v>
+        <v>8.051616738369518</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.336391671528631</v>
+        <v>4.349457191714237</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>8.328359541446645</v>
+        <v>8.341366053775033</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>8.246801375535021</v>
+        <v>8.259835656206754</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>7.784164681313477</v>
+        <v>7.797317254261472</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>4.556241072359668</v>
+        <v>4.569414542092417</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.123851414630884</v>
+        <v>2.137234835801593</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.8632873639811791</v>
+        <v>0.8767277299598106</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.6881171121433525</v>
+        <v>-0.674676511260607</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.637299010348571</v>
+        <v>-1.623748979740562</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.1992041963320119</v>
+        <v>0.1887745606338598</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>193</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-5.079264093645953</v>
+        <v>-5.068259927288096</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-7.209690759936187</v>
+        <v>-7.198903942440914</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.407746118067159</v>
+        <v>-1.394854812583006</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.821701812651099</v>
+        <v>1.835709370913555</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.021785416547061</v>
+        <v>-1.287486024607666</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-4.342886187763817</v>
+        <v>-4.32989610626916</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.256897434546204</v>
+        <v>1.269922278874439</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.2753683381934309</v>
+        <v>0.2885122164053158</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.888493938863569</v>
+        <v>-2.87532812686986</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-4.772582940708212</v>
+        <v>-4.759205733370862</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-4.978185385139916</v>
+        <v>-4.964749444196762</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.909737982064271</v>
+        <v>-3.896299784159936</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.741367091646886</v>
+        <v>-1.727817912123889</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.010407339704393</v>
+        <v>-2.020836975402666</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>221</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.2481940460329</v>
+        <v>2.261771764094831</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.06445690297803</v>
+        <v>-2.05203108619915</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.403245387215577</v>
+        <v>3.417966519656943</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.179493540025874</v>
+        <v>2.193802118608914</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4.349690409421193</v>
+        <v>4.364832210228478</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.196706752973171</v>
+        <v>4.209697984462743</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.661917551399732</v>
+        <v>3.674938691268139</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>5.004647003820544</v>
+        <v>5.017789322658267</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.139905372103861</v>
+        <v>3.153070188863204</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.841379928109731</v>
+        <v>1.854756251002776</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.881497311350557</v>
+        <v>-2.868064132105708</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.752351901847888</v>
+        <v>-3.738916059321184</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.816980116509562</v>
+        <v>-2.803432225197234</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.7584438201395329</v>
+        <v>-0.7688734558376851</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>204</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.908419425987006</v>
+        <v>1.922042488960948</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.3029987336090372</v>
+        <v>0.3163256586406433</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.860298007349719</v>
+        <v>1.874679624599139</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.012821601259446</v>
+        <v>1.026879383027072</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.42979248331077</v>
+        <v>-3.417533679339193</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.203258048014618</v>
+        <v>-0.190280835398184</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.265813781443171</v>
+        <v>-1.252805566574942</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.181205130639867</v>
+        <v>2.194338698076884</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.165871554182317</v>
+        <v>0.1790283597248035</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.1920528483733719</v>
+        <v>-0.1786827685508285</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.3953445564956368</v>
+        <v>-0.3819145872466692</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.340561731663804</v>
+        <v>-1.3271281817267</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.668531549838256</v>
+        <v>1.682078692266487</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.408976994340108</v>
+        <v>2.398547358641956</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>253</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.281360154157646</v>
+        <v>-3.269921026963075</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-4.105755683407594</v>
+        <v>-4.094394337431915</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.531558906929405</v>
+        <v>-2.518931118612294</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.613681440467467</v>
+        <v>-1.60061786412863</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.152353671243425</v>
+        <v>-2.139681039393267</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.039946266051103</v>
+        <v>-2.235763685410873</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-4.095464045302286</v>
+        <v>-4.082472246836161</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.379494529052259</v>
+        <v>-3.366377341698353</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-7.38319773183423</v>
+        <v>-7.370057731212569</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-8.628012854262671</v>
+        <v>-8.6146574558692</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-6.071983294022637</v>
+        <v>-6.058562893622138</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-4.460639869045792</v>
+        <v>-4.447211805448703</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-5.278277924414041</v>
+        <v>-5.264734131028227</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-8.193208543906728</v>
+        <v>-8.20363817960488</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>241</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.6131523312172362</v>
+        <v>0.6263549388419349</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.230068856684021</v>
+        <v>-2.218124442042786</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.6771880067733349</v>
+        <v>0.6914018063355982</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.045689691553719</v>
+        <v>2.060696092826312</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.991725582788419</v>
+        <v>4.00750982725117</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.45946198062078</v>
+        <v>3.475157069654351</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>4.204128126091156</v>
+        <v>4.217115691988639</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>5.396256107394763</v>
+        <v>5.409370668211366</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>6.169624430289097</v>
+        <v>6.1827659288316</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>7.396825805836741</v>
+        <v>7.410183948850431</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>7.19724854035158</v>
+        <v>7.210669145880871</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>7.235126956702743</v>
+        <v>7.248554541796352</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>5.573963400048029</v>
+        <v>5.587506653529047</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>4.996235964318139</v>
+        <v>4.985806328619887</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>239</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.444542949285591</v>
+        <v>-1.432379442900164</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.951800985346715</v>
+        <v>1.965977380944544</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.216078960018201</v>
+        <v>3.232164363219532</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>5.842296767068639</v>
+        <v>5.860166128326071</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>5.309121679698379</v>
+        <v>5.326466936969723</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.855122137604063</v>
+        <v>1.870618374699902</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.188948988938066</v>
+        <v>2.20191266748111</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.3585923427804687</v>
+        <v>-0.3455054234468449</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.505336684354553</v>
+        <v>2.518458212645932</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.748421863608357</v>
+        <v>3.76176385468915</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.712831323637658</v>
+        <v>2.726238243903794</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.6594853146710662</v>
+        <v>0.6729021582507997</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.075886016226924</v>
+        <v>1.089424388820731</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.7660168525710915</v>
+        <v>-0.7764464882691442</v>
       </c>
     </row>
     <row r="22">
@@ -1407,98 +1407,98 @@
         <v>198</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.484048740053716</v>
+        <v>-2.472700147897555</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-3.582948333044314</v>
+        <v>-3.57216516035318</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-8.508348333875354</v>
+        <v>-8.499333245745206</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-7.378649451406915</v>
+        <v>-7.368330444765846</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-5.901018899574872</v>
+        <v>-5.890049449295162</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-6.610145841493996</v>
+        <v>-6.599685815603117</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-6.195784270018329</v>
+        <v>-6.182874120982518</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-5.153029181909481</v>
+        <v>-5.13998185305423</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-7.225797354588373</v>
+        <v>-7.212718834991037</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-5.053275358009955</v>
+        <v>-5.039966244345052</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.737856104627504</v>
+        <v>-2.724470779558764</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-3.713148349920161</v>
+        <v>-3.699746033211078</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.136023701131798</v>
+        <v>-4.122492911506797</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.394350397222638</v>
+        <v>-4.40478003292079</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 7.909</t>
+          <t>X ≈ 7.908</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>229</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.641023980559339</v>
+        <v>1.655297434603867</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.344563657751529</v>
+        <v>1.358590928942199</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.808326832508484</v>
+        <v>1.82429274604835</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.062996831651773</v>
+        <v>1.079212342178714</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.833603841875764</v>
+        <v>1.850077944732362</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.341730724944391</v>
+        <v>-1.327908689808766</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.1247109939171409</v>
+        <v>-0.1118308576082612</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.021293778899491</v>
+        <v>-1.008278829927953</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.53379291364061</v>
+        <v>1.546853631662344</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.737112442697352</v>
+        <v>3.750408566593421</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>5.716842119655141</v>
+        <v>5.730217751445316</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>5.321004789101877</v>
+        <v>5.33440010797581</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.159196338944234</v>
+        <v>3.172722350425495</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.537412648077584</v>
+        <v>2.526983012379432</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>208</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.812209145011707</v>
+        <v>1.827390886150027</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.7362105145151361</v>
+        <v>-0.7237278053483678</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.145280773557488</v>
+        <v>-1.130925548493479</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.8833628042549293</v>
+        <v>0.9007758500338099</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.6005488806076968</v>
+        <v>-0.5850101718208407</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.038835017880338</v>
+        <v>3.057236150413168</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.477848622629409</v>
+        <v>2.490673409991267</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.802901522626172</v>
+        <v>-1.789957910473589</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.012994512664278</v>
+        <v>1.025999227119165</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.606186049336209</v>
+        <v>1.619434173167541</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.03088433200154839</v>
+        <v>-0.01755381463834027</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.006283134416385394</v>
+        <v>0.01964728639472213</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.4134532320714683</v>
+        <v>-0.3999425189237016</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.6453216481938284</v>
+        <v>-0.6557512838919806</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>178</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.8143150376756054</v>
+        <v>-0.8010090010134547</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.166717580769159</v>
+        <v>3.183582549416855</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.194702742876444</v>
+        <v>2.213583580676634</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-7.711329977188434</v>
+        <v>-7.701986340643543</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-4.895976004230782</v>
+        <v>-4.884374289606363</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-8.497261471161629</v>
+        <v>-8.489959772744918</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-6.363878820693415</v>
+        <v>-6.351226403267439</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.35800034083757</v>
+        <v>-2.345164789534046</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-5.206648769880864</v>
+        <v>-5.193766581822395</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.023255682638322</v>
+        <v>-1.010085984984457</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.221639843149802</v>
+        <v>-1.208370003013449</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.6241244575075413</v>
+        <v>-0.6108019359756369</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.322474695495309</v>
+        <v>2.335968259521145</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.012413874710226</v>
+        <v>2.001984239012074</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>164</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-3.688955194419485</v>
+        <v>-3.679432319857881</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.1509498209503803</v>
+        <v>0.1654009966266443</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.273246500094821</v>
+        <v>-0.2550320507708221</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.351174438844986</v>
+        <v>-1.334404369010677</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-3.68453730696141</v>
+        <v>-3.671926405105538</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-3.98452053800451</v>
+        <v>-3.973518910329503</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-5.894401174235277</v>
+        <v>-5.881956976026217</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-3.33146005974708</v>
+        <v>-3.318803254687126</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.249934539552612</v>
+        <v>0.2627058803624536</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.415687336476367</v>
+        <v>-2.402641167058341</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.398710622989455</v>
+        <v>-1.385534822300841</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.894976002433133</v>
+        <v>2.908247776995374</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.869952311427447</v>
+        <v>1.883415448173409</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>6.390325631355886</v>
+        <v>6.379895995657733</v>
       </c>
     </row>
     <row r="27">
@@ -1664,49 +1664,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.596058828646008</v>
+        <v>3.574577428172098</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>7.001821325296682</v>
+        <v>6.955985402585874</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.5655306233338635</v>
+        <v>-0.5823764275340721</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-2.581919223623345</v>
+        <v>-2.58334955113839</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.4674476185981291</v>
+        <v>0.4537557749382373</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>6.493133601397652</v>
+        <v>6.443324324978718</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.552886147899208</v>
+        <v>3.502617650162591</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.381527814576067</v>
+        <v>2.344910576126637</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.488619129246196</v>
+        <v>4.441090510399775</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.928936396364257</v>
+        <v>2.892672956317611</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.893592675692226</v>
+        <v>4.854270647640242</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.934955988081043</v>
+        <v>4.901610935315304</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.520351329064098</v>
+        <v>4.491826764819947</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.28109975648848</v>
+        <v>2.567823702272975</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>127</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.389743761399664</v>
+        <v>1.402266051075287</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-4.099465927250201</v>
+        <v>-4.086556117674149</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-6.83688877631937</v>
+        <v>-6.823881644901768</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-2.82123515973263</v>
+        <v>-2.808256017334166</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-3.350782765326308</v>
+        <v>-3.337671960951369</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.04898987317476866</v>
+        <v>0.06203276946913405</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-7.41905430461199</v>
+        <v>-7.791260155385977</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-5.543251200238231</v>
+        <v>-5.528782278189411</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-7.161001038825844</v>
+        <v>-7.14121247265561</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-8.794973894645779</v>
+        <v>-8.771028070111335</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-8.219411452805879</v>
+        <v>-8.192986754466403</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-6.625710877416545</v>
+        <v>-6.600770396307702</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-6.270572962299319</v>
+        <v>-6.245581804415949</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-4.446048480416778</v>
+        <v>-4.45647811611493</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>96</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-4.556057268360199</v>
+        <v>-4.543534978684576</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.053601073370835</v>
+        <v>2.066510882946886</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.689995422058949</v>
+        <v>4.703002553476551</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.325831378490442</v>
+        <v>-1.312852236091977</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.238031210921463</v>
+        <v>1.251142015296402</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.4832752189151464</v>
+        <v>0.4963181152095117</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.4236076484191358</v>
+        <v>0.4366739027196118</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.01664375469339774</v>
+        <v>-0.01786166767906394</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.008441457398249</v>
+        <v>2.005107167631031</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.1526045923925921</v>
+        <v>0.1566799257147196</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>4.10927731693036</v>
+        <v>4.107191569537321</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4.159938188855904</v>
+        <v>4.159958117953913</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>2.710726250299111</v>
+        <v>2.716169477054805</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>5.043780915908734</v>
+        <v>5.033351280210582</v>
       </c>
     </row>
     <row r="30">
@@ -1823,98 +1823,98 @@
         <v>78</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.126109629175787</v>
+        <v>-3.113587339500164</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-3.478662821442974</v>
+        <v>-3.465753011866923</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-7.669559381834162</v>
+        <v>-7.65655225041656</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-5.01705060967624</v>
+        <v>-5.004071467277775</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.5172827428819957</v>
+        <v>-0.5041719385070564</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.489398221254241</v>
+        <v>-1.476355324959876</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.561487544057513</v>
+        <v>-1.548421289757037</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.008340037728352</v>
+        <v>-2.00916773630928</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.010262681708419</v>
+        <v>2.994124101529913</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.3639312530026686</v>
+        <v>-0.3616208327788115</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.261402741711592</v>
+        <v>3.254622372161073</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>3.30706807190569</v>
+        <v>3.303913720301253</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>4.874187788760608</v>
+        <v>4.17073035214127</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>5.123909121036938</v>
+        <v>5.113479485338786</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 27.47</t>
+          <t>X ≈ 27.46</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>65</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.2619546336179113</v>
+        <v>-0.2494323439422885</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-6.367455372088237</v>
+        <v>-6.354545562512186</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-3.859251918646741</v>
+        <v>-3.846244787229139</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-8.202286076664038</v>
+        <v>-8.189306934265574</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.240508831785384</v>
+        <v>-1.227398027410445</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.9946664812730006</v>
+        <v>-0.9816235849786352</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.017480693901362</v>
+        <v>-1.004414439600886</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.589036000592557</v>
+        <v>1.555428085938409</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.974731875614331</v>
+        <v>-2.984801956136344</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>2.318612361653983</v>
+        <v>2.294652878018255</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3.681757066448363</v>
+        <v>3.653567857298157</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.679057784320932</v>
+        <v>0.6734959722893521</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>3.335726250299153</v>
+        <v>3.349282296650756</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>2.046986044113865</v>
+        <v>2.036556408415713</v>
       </c>
     </row>
     <row r="32">
@@ -1927,98 +1927,98 @@
         <v>41</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.346521704257817</v>
+        <v>3.35904399393344</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>8.85946670490074</v>
+        <v>8.872376514476791</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-5.872747247278319</v>
+        <v>-5.859740115860717</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-3.297008162107232</v>
+        <v>-3.284029019708768</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-8.620431660264828</v>
+        <v>-8.607320855889888</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-6.054119806721751</v>
+        <v>-6.041076910427385</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-8.39006183614778</v>
+        <v>-8.376995581847304</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-4.083221601759085</v>
+        <v>-4.112046753569551</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-11.25092177241615</v>
+        <v>-11.22173715677424</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-14.49695754740862</v>
+        <v>-14.43346858810231</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-14.75611465943193</v>
+        <v>-14.68825357801598</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-17.21962889485355</v>
+        <v>-17.11565145171611</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-12.76183472531064</v>
+        <v>-12.74827867895904</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-24.70723534425387</v>
+        <v>-24.71766497995202</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 32.36</t>
+          <t>X ≈ 32.35</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>37</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.214842107869103</v>
+        <v>1.227364397544726</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-8.142870501234157</v>
+        <v>-8.129960691658106</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-11.26959378532288</v>
+        <v>-11.25658665390527</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-5.855401392266081</v>
+        <v>-5.842422249867617</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-11.61783856960923</v>
+        <v>-11.60472776523429</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-21.8283518546139</v>
+        <v>-21.81530895831953</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-19.12130769621569</v>
+        <v>-19.10824144191522</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-17.08119933276259</v>
+        <v>-17.02322540274477</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-9.21339491948423</v>
+        <v>-9.191333082863245</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-7.362502233742553</v>
+        <v>-7.32835796938793</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-10.27256887647491</v>
+        <v>-10.20691009177366</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-4.892667787404619</v>
+        <v>-4.837449594849687</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-10.71832780375492</v>
+        <v>-10.70477175740332</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-7.765903768775949</v>
+        <v>-7.776333404474101</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>28</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-6.224305667148741</v>
+        <v>-6.211783377473118</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.400090107642114</v>
+        <v>2.412999917218166</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-1.56620717038308</v>
+        <v>-1.553200038965478</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-1.329661520768767</v>
+        <v>-1.316682378370302</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-1.868082735840936</v>
+        <v>-1.854971931465997</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1.676933315132089</v>
+        <v>-1.663890418837724</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1.916054056031015</v>
+        <v>1.929120310331491</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-1.915171556835702</v>
+        <v>-2.003084387876996</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-5.256783210259208</v>
+        <v>-5.275450414131342</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.9721255051833424</v>
+        <v>0.9210675274242135</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-2.693746211445372</v>
+        <v>-2.679763053294884</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-6.244019138756016</v>
+        <v>-6.13797425744329</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.478583393156228</v>
+        <v>0.4921394395078309</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that RSI Divergence-7-14 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that RSI Divergence-7-14 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4080</v>
+        <v>4081</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.1357544697335555</v>
+        <v>-0.1360210622881368</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.2193814346405105</v>
+        <v>-0.2196369391369117</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1366442672457637</v>
+        <v>-0.1369223842085532</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.05580036569730851</v>
+        <v>0.05547581025346915</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.05356107244336528</v>
+        <v>-0.05386212323951867</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03714272624338122</v>
+        <v>0.03682104696651578</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.08811924863607601</v>
+        <v>0.08778446092323833</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.1482935247812662</v>
+        <v>0.1479411801676775</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.02739420590014419</v>
+        <v>0.02707093849352304</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.02565680723927244</v>
+        <v>-0.02597211830482138</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.04524040533482321</v>
+        <v>-0.04555225018747677</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.05191422724107753</v>
+        <v>0.05157863122790474</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.06050016479522924</v>
+        <v>-0.06081079497103303</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.09102300565989907</v>
+        <v>-0.09075024719282965</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4053</v>
+        <v>4054</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2061781136187264</v>
+        <v>-0.2065122931357735</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.3534744177990703</v>
+        <v>-0.3537843665888332</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2922034744164961</v>
+        <v>-0.292531564933789</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.07477148944242629</v>
+        <v>-0.07515230177272514</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.08283946571161493</v>
+        <v>-0.08322243668899887</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.01814187439916992</v>
+        <v>-0.01853877744260046</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.03372353761675839</v>
+        <v>0.03331304627837284</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.09739233495238864</v>
+        <v>0.09696252744083722</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.0239180696538952</v>
+        <v>-0.02431864228254454</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.1209745818405281</v>
+        <v>-0.1213576933178047</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1146942093164043</v>
+        <v>-0.115080570545004</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.01713874418139483</v>
+        <v>-0.01754909855659292</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1275199263165803</v>
+        <v>-0.1279063593295575</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.184599296279778</v>
+        <v>-0.1842321764577335</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4010</v>
+        <v>4011</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.3184445344779405</v>
+        <v>-0.3188881975323667</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.4749771246212688</v>
+        <v>-0.4753981713237536</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.4088585059732637</v>
+        <v>-0.4093001617594894</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.2153986514419231</v>
+        <v>-0.215887360039666</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1929454627181997</v>
+        <v>-0.1934453805471179</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.0809900597811577</v>
+        <v>-0.08151511987513516</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02767806713937659</v>
+        <v>-0.02821750284255131</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.04165936635865819</v>
+        <v>0.04109773605546252</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.1301240358219076</v>
+        <v>-0.1306437729007541</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.1942269488640633</v>
+        <v>-0.1947394854759708</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.2106225801781676</v>
+        <v>-0.2111333431983837</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.0625635056552909</v>
+        <v>-0.06311108128431897</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.2444283246198609</v>
+        <v>-0.2449350513054185</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.2300137640580218</v>
+        <v>-0.2295195749377683</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3947</v>
+        <v>3948</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.3722261989978506</v>
+        <v>-0.3728625086964357</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.5308770506281348</v>
+        <v>-0.5314960629921188</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.5584961021255452</v>
+        <v>-0.5591139731170429</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3893394101201082</v>
+        <v>-0.389998541621857</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2568859315378234</v>
+        <v>-0.2575863889244872</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1731857984262746</v>
+        <v>-0.1739036253336508</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1429884532336914</v>
+        <v>-0.1437154611452414</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.01076221124020549</v>
+        <v>0.009989430421178724</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.2640096167154198</v>
+        <v>-0.2647141193923446</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.3662331276937394</v>
+        <v>-0.3669240060743348</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.2530858404052125</v>
+        <v>-0.2538085812320006</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.1538697338433508</v>
+        <v>-0.1546174829472733</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.2306364649997761</v>
+        <v>-0.2313710333062389</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2959813507917204</v>
+        <v>-0.2952961362027935</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3875</v>
+        <v>3876</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.4101049868766395</v>
+        <v>-0.4109751717017431</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.6190330291351316</v>
+        <v>-0.6198799013759597</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.7170705522772494</v>
+        <v>-0.717900006938244</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.5214936590294741</v>
+        <v>-0.5223714733598186</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3251444997844146</v>
+        <v>-0.3260833490059909</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2196719403271885</v>
+        <v>-0.2206328892553344</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.2131148449142088</v>
+        <v>-0.2140795526680463</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.04786273077201741</v>
+        <v>-0.04887921276213802</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.300843374384776</v>
+        <v>-0.3017963180923076</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.3891942154033288</v>
+        <v>-0.3901407513475021</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.2959371078600626</v>
+        <v>-0.2969120041957822</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.2729074544640113</v>
+        <v>-0.2738881496748675</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.3175245236947006</v>
+        <v>-0.3185020727070409</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.3629395141987928</v>
+        <v>-0.3620305567347302</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3769</v>
+        <v>3770</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.6690068024944793</v>
+        <v>-0.6564845128188566</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.6799920971520166</v>
+        <v>-0.6812084165648713</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.9019970418872205</v>
+        <v>-0.9031654946002448</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.7840228498465649</v>
+        <v>-0.7852197933362888</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.5406585687151164</v>
+        <v>-0.5419344777970423</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.4406306129550899</v>
+        <v>-0.4419259845727339</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.5110184678938055</v>
+        <v>-0.5122980759268927</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.2221265495802385</v>
+        <v>-0.2234954336512516</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.56003677032772</v>
+        <v>-0.5613184252845898</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.6005506415426538</v>
+        <v>-0.6018442680843705</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.5254860712869984</v>
+        <v>-0.5268055907824021</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.3967637688275829</v>
+        <v>-0.398117221191761</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.3778016011597813</v>
+        <v>-0.3791716943331167</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.4050008122242872</v>
+        <v>-0.4037618939715557</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3663</v>
+        <v>3664</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.5206492045637177</v>
+        <v>-0.5081269148880949</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.5812024093646997</v>
+        <v>-0.5682925997886485</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.9070662685133399</v>
+        <v>-0.9086422158362097</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.7349964154127022</v>
+        <v>-0.7366157028160316</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.5779833627583741</v>
+        <v>-0.5796642995648824</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.5109064303928861</v>
+        <v>-0.5125965679640316</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.5536511284951118</v>
+        <v>-0.5553333594502234</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.2974380461173567</v>
+        <v>-0.2992066514963483</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.5070570473884146</v>
+        <v>-0.5087714909736718</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.5514237195340499</v>
+        <v>-0.5531555126151986</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.4682549965924139</v>
+        <v>-0.4700172685488226</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.3640737090151944</v>
+        <v>-0.3658641768225692</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.3051034440240343</v>
+        <v>-0.3069250703342732</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.4221964250686128</v>
+        <v>-0.4206152408956854</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3529</v>
+        <v>3530</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.403042839983982</v>
+        <v>-0.3905205503083593</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.7999271874115195</v>
+        <v>-0.7870173778354683</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.9970557810137635</v>
+        <v>-0.9840486495961613</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.5973754585620199</v>
+        <v>-0.5995862178722078</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.6118361727725201</v>
+        <v>-0.6140676155152534</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.6383138809292177</v>
+        <v>-0.6405260137200912</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.7360644836925658</v>
+        <v>-0.7382538912575356</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.3959043814788501</v>
+        <v>-0.3982116695589113</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.6394830397270539</v>
+        <v>-0.6417253306865831</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.6533262998336582</v>
+        <v>-0.6556032102883336</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.530950427471744</v>
+        <v>-0.533272203070517</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.4807792633665855</v>
+        <v>-0.483114981406203</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.4036505202391325</v>
+        <v>-0.4060278137995823</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.4780264893996673</v>
+        <v>-0.4759735545391806</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3388</v>
+        <v>3389</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.5664009562794021</v>
+        <v>-0.5538786666037794</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.001157858446369</v>
+        <v>-0.988248048870318</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.042981551803777</v>
+        <v>-1.029974420386175</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.6027057885052898</v>
+        <v>-0.6055450990984781</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.7131708888530994</v>
+        <v>-0.7160091362242937</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.8709130271582239</v>
+        <v>-0.873689881749165</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.9692727551058056</v>
+        <v>-0.9720268976683073</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.5072498876095608</v>
+        <v>-0.5101676335464163</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.8173935185566776</v>
+        <v>-0.8202248710185955</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.5017150095196854</v>
+        <v>-0.5046882885754513</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.4836514851312046</v>
+        <v>-0.4866431155987527</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.3148155989329737</v>
+        <v>-0.3178567350255577</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.4530019881193041</v>
+        <v>-0.4560274378625593</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.4228168802345209</v>
+        <v>-0.4202608964393661</v>
       </c>
     </row>
     <row r="15">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3206</v>
+        <v>3207</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.4411995142398197</v>
+        <v>-0.428677224564197</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.9644646694926422</v>
+        <v>-0.9515548599165911</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.9551045203678399</v>
+        <v>-0.9420973889502378</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.5450006414916757</v>
+        <v>-0.5320214990932115</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.631221350540315</v>
+        <v>-0.6349876691043335</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.7213721858888462</v>
+        <v>-0.7250911043996453</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.7270865335381416</v>
+        <v>-0.7308118952825424</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.3991366029397412</v>
+        <v>-0.4029999096412737</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.6299392336571827</v>
+        <v>-0.6337372520352744</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.5596302801950515</v>
+        <v>-0.5635138534738928</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.3108111462104901</v>
+        <v>-0.3147892391513309</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.1654655227958841</v>
+        <v>-0.1694886325226292</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.06932519965411643</v>
+        <v>-0.07341097018220211</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.2074407517976482</v>
+        <v>-0.2042149810928251</v>
       </c>
     </row>
     <row r="16">
@@ -2734,49 +2734,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3017</v>
+        <v>3018</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.7920838438307172</v>
+        <v>-0.7795615541550944</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.21436112379201</v>
+        <v>-1.201451314215959</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.080653682387272</v>
+        <v>-1.06764655096967</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.082544586780102</v>
+        <v>-1.069565444381638</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.9424175259367473</v>
+        <v>-0.9471348124756815</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.288292734933059</v>
+        <v>-1.292871224643179</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.289255845707459</v>
+        <v>-1.293844495425517</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.9117796068256752</v>
+        <v>-0.9165386584741384</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.9548275590921094</v>
+        <v>-0.9595807540532135</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.727737022098303</v>
+        <v>-0.732646226659142</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.3843625610020851</v>
+        <v>-0.3894071010340383</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.1327240079179646</v>
+        <v>-0.1378516182477938</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.02890053790679303</v>
+        <v>0.0236777918477955</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.2329150292906945</v>
+        <v>-0.2288256581592094</v>
       </c>
     </row>
     <row r="17">
@@ -2786,49 +2786,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2824</v>
+        <v>2825</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.4990860434715358</v>
+        <v>-0.4865637537959131</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.8046236522000001</v>
+        <v>-0.7917138426239489</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.058299277257589</v>
+        <v>-1.045292145839987</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.281028848497606</v>
+        <v>-1.268049706099141</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.9369933039509846</v>
+        <v>-0.9238824995760453</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.079533338192149</v>
+        <v>-1.085385984942725</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.463267029520829</v>
+        <v>-1.46899741133344</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.9929125931531146</v>
+        <v>-0.998866027979183</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.8226754304462602</v>
+        <v>-0.8286996061050331</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.4513010227032197</v>
+        <v>-0.4575573824837846</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.07040795581136194</v>
+        <v>-0.07682619051000472</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.1254076128363693</v>
+        <v>0.1189202387508175</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.149885542334502</v>
+        <v>0.1433374983492257</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.1114362701158171</v>
+        <v>-0.1063979823262926</v>
       </c>
     </row>
     <row r="18">
@@ -2838,49 +2838,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2603</v>
+        <v>2604</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.7323357168409075</v>
+        <v>-0.7198134271652847</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.6976612440471257</v>
+        <v>-0.6847514344710746</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.437093503476788</v>
+        <v>-1.424086372059186</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.574834245295023</v>
+        <v>-1.561855102896558</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.385843515497363</v>
+        <v>-1.372732711122424</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.52749686494878</v>
+        <v>-1.534776751931432</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.898405635891727</v>
+        <v>-1.905560344772368</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.502117614640305</v>
+        <v>-1.509496147983356</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.159106608841796</v>
+        <v>-1.166630145539742</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.6459543035828403</v>
+        <v>-0.653802126339599</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.1682592541671895</v>
+        <v>0.1600645871753557</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.4546372911864296</v>
+        <v>0.4463326127423315</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.4017784776416562</v>
+        <v>0.3934281699712514</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.05650401173885911</v>
+        <v>-0.05017406541153946</v>
       </c>
     </row>
     <row r="19">
@@ -2890,49 +2890,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.9568934697116447</v>
+        <v>-0.9443711800360219</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.7827527969616099</v>
+        <v>-0.7698429873855588</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.717488613192749</v>
+        <v>-1.704481481775147</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.794876676598534</v>
+        <v>-1.78189753420007</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.212035433198942</v>
+        <v>-1.198924628824003</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.640104084062827</v>
+        <v>-1.649058904836764</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.952198357153712</v>
+        <v>-1.961044500919137</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.815330553380264</v>
+        <v>-1.824322109898489</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.27177669856956</v>
+        <v>-1.281011118487221</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.6845520096531743</v>
+        <v>-0.6941872717516446</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.2161855473623646</v>
+        <v>0.2061328170012189</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.6072928145967822</v>
+        <v>0.5970767802721966</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.2940595836324462</v>
+        <v>0.2838928755761643</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.2661572527726577</v>
+        <v>-0.2583153864560899</v>
       </c>
     </row>
     <row r="20">
@@ -2942,49 +2942,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.6828533619927128</v>
+        <v>-0.6703310723170901</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.39099150606188</v>
+        <v>-0.3780816964858289</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.621514808758747</v>
+        <v>-1.608507677341144</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.816238463523582</v>
+        <v>-1.803259321125118</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.101177784445326</v>
+        <v>-1.088066980070387</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.592965187491046</v>
+        <v>-1.579922291196681</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.699520715447477</v>
+        <v>-1.711057905801759</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.630925387562463</v>
+        <v>-1.642608102611398</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.5512783195313702</v>
+        <v>-0.5634848991022636</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.2519324235649947</v>
+        <v>0.2391517858085521</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.9575213893336638</v>
+        <v>0.9443573231901894</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.204770432938616</v>
+        <v>1.191489920555092</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.9510033811794045</v>
+        <v>0.9377366728145944</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.668392596554888</v>
+        <v>0.6779522738451007</v>
       </c>
     </row>
     <row r="21">
@@ -2994,49 +2994,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.846809987747875</v>
+        <v>-0.8342876980722522</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.1583313267968123</v>
+        <v>-0.1454215172207611</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.91232183161609</v>
+        <v>-1.899314700198488</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.304807852171166</v>
+        <v>-2.291828709772702</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.745476845601935</v>
+        <v>-1.732366041226996</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.232143637630131</v>
+        <v>-2.219100741335765</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.446386526896717</v>
+        <v>-2.460632846550702</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.519928400835255</v>
+        <v>-2.534280129772092</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.401534257960101</v>
+        <v>-1.4164998254045</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.6519622247958878</v>
+        <v>-0.6675736870629478</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.1681385844017314</v>
+        <v>0.1520272343819755</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.4418749357065153</v>
+        <v>0.4256176363372859</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.3661564706558735</v>
+        <v>0.3498066804996967</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.1208806534415316</v>
+        <v>0.1332550927324405</v>
       </c>
     </row>
     <row r="22">
@@ -3046,49 +3046,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.7610607813808201</v>
+        <v>-0.7485384917051974</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.4610453859818762</v>
+        <v>-0.448135576405825</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.648028787918975</v>
+        <v>-2.635021656501372</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.473570159493072</v>
+        <v>-3.460591017094607</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.757511087826892</v>
+        <v>-2.744400283451952</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.818492089179337</v>
+        <v>-2.805449192884971</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-3.111359629108314</v>
+        <v>-3.129108178196539</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.829988015406144</v>
+        <v>-2.848087661152853</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.962003738880391</v>
+        <v>-1.980659976030807</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.283229810107187</v>
+        <v>-1.302613682551112</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.1969163763890123</v>
+        <v>-0.2170408107744279</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.4106571202368201</v>
+        <v>0.3901641265968365</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.2643405274436859</v>
+        <v>0.2437667091207416</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.2481126486018042</v>
+        <v>0.2636802144237294</v>
       </c>
     </row>
     <row r="23">
@@ -3098,101 +3098,101 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.5286686725135041</v>
+        <v>-0.5161463828378814</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.03997128276773054</v>
+        <v>-0.0270614731916794</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.857604217006596</v>
+        <v>-1.844597085588994</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.94686327952104</v>
+        <v>-2.933884137122575</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.333522976978045</v>
+        <v>-2.320412172603106</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.307083749289482</v>
+        <v>-2.294040852995117</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.69534050179211</v>
+        <v>-2.717504599795163</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.516662299488125</v>
+        <v>-2.539173399752947</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.252037025045119</v>
+        <v>-1.275453948750943</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.7747359283055815</v>
+        <v>-0.798872493146618</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.1457989275559584</v>
+        <v>0.1209245628261968</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.9668652149855106</v>
+        <v>0.9414249922482867</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.8578501441044182</v>
+        <v>0.8322754939296217</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.8742759204500601</v>
+        <v>0.8929212824796977</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 9.131</t>
+          <t>X &gt; 9.13</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.9296853129926603</v>
+        <v>-0.9171630233170376</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.2958699925166499</v>
+        <v>-0.2829601829405988</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.535165323010595</v>
+        <v>-2.522158191592993</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-3.687991580940391</v>
+        <v>-3.675012438541927</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.103718329292427</v>
+        <v>-3.090607524917488</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.485506543942449</v>
+        <v>-2.472463647648084</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-3.170460887024852</v>
+        <v>-3.1987137021829</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.79304598892702</v>
+        <v>-2.821895058212561</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.766932146884528</v>
+        <v>-1.796670429327257</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.608644949257695</v>
+        <v>-1.639021979179248</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.8838773363590633</v>
+        <v>-0.9149852276526644</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.162104954717023</v>
+        <v>0.1301416845856949</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.4325004438474949</v>
+        <v>0.4000478083348327</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.5668842250289856</v>
+        <v>0.5911469791353099</v>
       </c>
     </row>
     <row r="25">
@@ -3202,49 +3202,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.482851217226333</v>
+        <v>-1.47032892755071</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.2070331073801981</v>
+        <v>-0.1941232978041469</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.815568801464757</v>
+        <v>-2.802561670047155</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-4.610243484064185</v>
+        <v>-4.597264341665721</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-3.608722446970816</v>
+        <v>-3.595611642595877</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-3.600019681536189</v>
+        <v>-3.586976785241824</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-4.309984047071488</v>
+        <v>-4.345411879830415</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.992803553418355</v>
+        <v>-3.029882390314988</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.327770891003013</v>
+        <v>-2.36558059264204</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.257223851010892</v>
+        <v>-2.295765079652249</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.055965158770661</v>
+        <v>-1.095862876787336</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.1935413646321962</v>
+        <v>0.1524118733683721</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.6031681107642299</v>
+        <v>0.5612861688675537</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.811441762982767</v>
+        <v>0.8424598073423653</v>
       </c>
     </row>
     <row r="26">
@@ -3254,49 +3254,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.622358180837146</v>
+        <v>-1.609835891161524</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.9110514221405523</v>
+        <v>-0.8981416125645012</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-3.861088537564093</v>
+        <v>-3.848081406146491</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-3.963123442122672</v>
+        <v>-3.950144299724208</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-3.340104471364413</v>
+        <v>-3.326993666989473</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-2.578086459316573</v>
+        <v>-2.565043563022208</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.881387013420024</v>
+        <v>-3.927338126701848</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-3.125271281248821</v>
+        <v>-3.172598705231863</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.727020290252412</v>
+        <v>-1.776099203796491</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.514722484035879</v>
+        <v>-2.563740347627508</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.021392950307025</v>
+        <v>-1.072412913709755</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.3641679957469321</v>
+        <v>0.3114892247304795</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.2443913556855222</v>
+        <v>0.1913875598086037</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.5608285907817248</v>
+        <v>0.6007790709990246</v>
       </c>
     </row>
     <row r="27">
@@ -3306,49 +3306,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.130454102132497</v>
+        <v>-1.117931812456874</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.163835462585993</v>
+        <v>-1.150925653009942</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-4.715088674204104</v>
+        <v>-4.702081542786502</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-4.584835541596604</v>
+        <v>-4.57185639919814</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-3.258120458246971</v>
+        <v>-3.245009653872032</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-2.243318405753691</v>
+        <v>-2.230275509459325</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-3.402237053516245</v>
+        <v>-3.462762052369683</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-3.076192965321809</v>
+        <v>-3.137848638404812</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.197587187332282</v>
+        <v>-2.260684760031367</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.538295436430303</v>
+        <v>-2.602030587646851</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.9315814868528633</v>
+        <v>-0.9979897354359366</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.2382304267444155</v>
+        <v>-0.3057113587063967</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.1425346192661081</v>
+        <v>-0.2107755904694031</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.8267439994275065</v>
+        <v>-0.7728081400792775</v>
       </c>
     </row>
     <row r="28">
@@ -3361,98 +3361,98 @@
         <v>551</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-2.314226850675929</v>
+        <v>-2.301704561000307</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-3.208954585503982</v>
+        <v>-3.19604477592793</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-5.754360926509172</v>
+        <v>-5.74135379509157</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-5.086473385299527</v>
+        <v>-5.073494242901063</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.191202844099294</v>
+        <v>-4.178092039724355</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-4.431395314985785</v>
+        <v>-4.41835241869142</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-5.14417353590342</v>
+        <v>-5.219908656093786</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-4.443099440141957</v>
+        <v>-4.520976643522545</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-3.872172435404565</v>
+        <v>-3.951332242045751</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-3.907583989834386</v>
+        <v>-3.988171772058934</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.390518028470318</v>
+        <v>-2.474331283979652</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.533874211219754</v>
+        <v>-1.619355276798984</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.310371753330656</v>
+        <v>-1.39709451494349</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.605115030854734</v>
+        <v>-1.615544666552886</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 21.36</t>
+          <t>X &gt; 21.35</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>424</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-3.423670878349512</v>
+        <v>-3.411148588673889</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.942221235499808</v>
+        <v>-2.929311425923757</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-5.430113197910359</v>
+        <v>-5.417106066492757</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-5.764976344372627</v>
+        <v>-5.751997201974163</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-4.442932443165724</v>
+        <v>-4.429821638790784</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-5.773397482194255</v>
+        <v>-5.76035458589989</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-4.462782362257222</v>
+        <v>-4.449716107956746</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-4.113572851622557</v>
+        <v>-4.219110333138843</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-2.887075188625076</v>
+        <v>-2.99587283334894</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.443672390987579</v>
+        <v>-2.555570946934751</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.6445994792000036</v>
+        <v>-0.7614321218291451</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.008725021108929809</v>
+        <v>-0.12728046505935</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.1753488918085466</v>
+        <v>0.05516464959188738</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7541750589340381</v>
+        <v>-0.7646046946321903</v>
       </c>
     </row>
     <row r="30">
@@ -3465,98 +3465,98 @@
         <v>328</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.092240715419557</v>
+        <v>-3.079718425743934</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-4.404413130779027</v>
+        <v>-4.391503321202975</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-8.392096208633092</v>
+        <v>-8.37908907721549</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-7.064238285606436</v>
+        <v>-7.051259143207972</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-6.105653512654655</v>
+        <v>-6.092542708279716</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-7.604618760567739</v>
+        <v>-7.591575864273373</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-5.892945292211273</v>
+        <v>-5.879879037910797</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-5.312674050723764</v>
+        <v>-5.448744088883167</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-4.319909328924588</v>
+        <v>-4.459574297050395</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-3.203558337342749</v>
+        <v>-3.349400470637029</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-2.035978053677169</v>
+        <v>-2.186395153448601</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.228821570366925</v>
+        <v>-1.382082001551034</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.5667127740911297</v>
+        <v>-0.7236660316167658</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.451137783278256</v>
+        <v>-2.461567418976408</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 26.25</t>
+          <t>X &gt; 26.24</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>250</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-3.08167361432762</v>
+        <v>-3.069151324651997</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-4.693247227291877</v>
+        <v>-4.680337417715826</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-8.617527698594351</v>
+        <v>-8.604520567176749</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-7.702960840496658</v>
+        <v>-7.689981698098194</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-7.849225192823731</v>
+        <v>-7.836114388448792</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-9.512567568833553</v>
+        <v>-9.499524672539188</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-7.244360109635252</v>
+        <v>-7.231293855334776</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-6.343626262778336</v>
+        <v>-6.521891910886218</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-6.606922996242076</v>
+        <v>-6.785128197407452</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-4.089521987656852</v>
+        <v>-4.281587717648797</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-3.688760861838475</v>
+        <v>-3.883992621438814</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-2.644019138755986</v>
+        <v>-2.84411266676895</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-2.264273749700884</v>
+        <v>-2.250717703349281</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-4.814552417424601</v>
+        <v>-4.824982053122753</v>
       </c>
     </row>
     <row r="32">
@@ -3569,98 +3569,98 @@
         <v>185</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-4.07238568863103</v>
+        <v>-4.059863398955407</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-10.28935432398135</v>
+        <v>-10.27634719256375</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-7.527522244005425</v>
+        <v>-7.514543101606961</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-10.17120661697233</v>
+        <v>-10.1580958125974</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-12.5053436266251</v>
+        <v>-12.49230073033073</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-9.432182607055267</v>
+        <v>-9.419116352754791</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-9.130777868827579</v>
+        <v>-9.359869207067845</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-7.883098254841016</v>
+        <v>-8.12037795785406</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-6.341028650928223</v>
+        <v>-6.592158737748029</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.532324681535584</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-3.81158670632356</v>
+        <v>-4.080029215627277</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-4.231841317268461</v>
+        <v>-4.218285270916859</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-7.225363228235409</v>
+        <v>-7.235792863933561</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 31.14</t>
+          <t>X &gt; 31.13</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>144</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-6.184713487995211</v>
+        <v>-6.172191198319588</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-7.796287100959468</v>
+        <v>-7.783377291383417</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-11.54686050554263</v>
+        <v>-11.53385337412503</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-8.732043614545873</v>
+        <v>-8.719064472147409</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-10.61274670881267</v>
+        <v>-10.59963590443773</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-14.34215040868091</v>
+        <v>-14.32910751238654</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-9.728897548771975</v>
+        <v>-9.715831294471499</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-10.56792930597901</v>
+        <v>-10.85404087785555</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-6.92420405886476</v>
+        <v>-7.237352074828181</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-4.018854451235896</v>
+        <v>-4.359563572022161</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-3.864609192653141</v>
+        <v>-4.210150481843257</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.005980861244012203</v>
+        <v>-0.3684978845186393</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.803162638589775</v>
+        <v>-1.789606592238172</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-2.247885750757938</v>
+        <v>-2.25831538645609</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>107</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-8.743438320209975</v>
+        <v>-8.730916030534353</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-7.676440504602802</v>
+        <v>-7.663530695026751</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-11.64273778262797</v>
+        <v>-11.62973065121037</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-9.726770364306176</v>
+        <v>-9.713791221907712</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-10.26519157937835</v>
+        <v>-10.25208077500341</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-11.75346392737698</v>
+        <v>-11.74042103108261</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-6.481054787506395</v>
+        <v>-6.467988533205919</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-8.315677053726766</v>
+        <v>-8.720771462706942</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-6.132614695846819</v>
+        <v>-6.561676399152496</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-2.862639797471907</v>
+        <v>-3.332971116858289</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-1.648772666471793</v>
+        <v>-2.136504635418724</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>1.699906094888867</v>
+        <v>1.176840557371527</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>1.279651483943965</v>
+        <v>1.293207530295568</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.3397860622844178</v>
+        <v>-0.3502156979825699</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>79</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-9.636295463067121</v>
+        <v>-9.623773173391498</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-11.24786907603138</v>
+        <v>-11.23495926645533</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-15.21416635405654</v>
+        <v>-15.20115922263894</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-12.70296084049665</v>
+        <v>-12.68998169809819</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-13.24138205556882</v>
+        <v>-13.22827125119388</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-15.32489249880555</v>
+        <v>-15.31184960251118</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-9.457245263696869</v>
+        <v>-9.444179009396393</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-10.58421064756156</v>
+        <v>-11.10172384365933</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-6.443035981877863</v>
+        <v>-7.017553963463797</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-4.221797119931992</v>
+        <v>-4.840731649009058</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-1.278402296101412</v>
+        <v>-1.943957348070214</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>4.515474532130092</v>
+        <v>3.769433149964122</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>1.563574351564931</v>
+        <v>1.577130397916534</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>1.813295683841218</v>
+        <v>1.802866048143066</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that RSI Divergence-7-14 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that RSI Divergence-7-14 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7.03037120359955</v>
+        <v>7.042893493275173</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>16.13308330492099</v>
+        <v>16.14599311449705</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>9.78583364594347</v>
+        <v>9.798840777361072</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.582753445217634</v>
+        <v>1.595732587616098</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>6.996713182526413</v>
+        <v>7.009823986901353</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.722726548813505</v>
+        <v>3.73576944510787</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2.447516641065029</v>
+        <v>2.460582895365505</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-1.591095329145041</v>
+        <v>-1.577914319849803</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>5.490761927529796</v>
+        <v>5.503960666484559</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>8.212065313930452</v>
+        <v>8.225470441583283</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>9.197788180089063</v>
+        <v>9.211245473799281</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>4.47026657552972</v>
+        <v>4.48371886424983</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>10.00239291696577</v>
+        <v>10.01594896331737</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>10.25211424924206</v>
+        <v>10.2416846135439</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>111</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7.866922040150392</v>
+        <v>7.879444329826015</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>17.06615923799693</v>
+        <v>17.07906904757299</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>13.06768692779674</v>
+        <v>13.08069405921434</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.990732853197045</v>
+        <v>6.003711995595509</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6.353212539025762</v>
+        <v>6.366323343400701</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4.848852674939629</v>
+        <v>4.861895571233994</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.863218056766449</v>
+        <v>3.876284311066925</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.6933319552822397</v>
+        <v>0.7065129645774775</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>6.037737474505342</v>
+        <v>6.050936213460105</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>9.692116793981938</v>
+        <v>9.705521921634769</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>9.487363469664359</v>
+        <v>9.500820763374577</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>5.918143023406174</v>
+        <v>5.931595312126284</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>10.00239291696577</v>
+        <v>10.01594896331737</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>11.15301515014296</v>
+        <v>11.14258551444481</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>154</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8.545522718751059</v>
+        <v>8.558045008426681</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>15.37550754734524</v>
+        <v>15.38841735692129</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>12.38323624334606</v>
+        <v>12.39624337476366</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7.968034830499015</v>
+        <v>7.981013972897479</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7.429613615426845</v>
+        <v>7.442724419801785</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.129652955739907</v>
+        <v>5.142695852034272</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.395568589116984</v>
+        <v>4.40863484341746</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.980333242283528</v>
+        <v>1.993514251578766</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>7.114138550906425</v>
+        <v>7.127337289861188</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8.86141596328109</v>
+        <v>8.874821090933921</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>9.306013288314176</v>
+        <v>9.319470582024394</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>5.444292549555705</v>
+        <v>5.457744838275815</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>10.21884313341599</v>
+        <v>10.2323991797676</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>9.169863166990993</v>
+        <v>9.159433531292841</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>217</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.953566288084957</v>
+        <v>6.96608857776058</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>11.79360557834651</v>
+        <v>11.80651538792256</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>11.39873687174992</v>
+        <v>11.41174400316752</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>8.764013045832073</v>
+        <v>8.776992188230537</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>6.382273858409668</v>
+        <v>6.395384662784608</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.297227316862653</v>
+        <v>5.310270213157018</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>5.212493599590374</v>
+        <v>5.22555985389085</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.980333242283528</v>
+        <v>1.993514251578766</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>7.449287273151917</v>
+        <v>7.46248601210668</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>9.364139046649342</v>
+        <v>9.377544174302173</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>7.316067749981535</v>
+        <v>7.329525043691753</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>5.507132934976731</v>
+        <v>5.520585223696841</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.930196296382064</v>
+        <v>6.943752342733667</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>7.640747121745903</v>
+        <v>7.630317486047751</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>289</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5.638049569063384</v>
+        <v>5.650571858739006</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>9.908828897275605</v>
+        <v>9.921738706851656</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>10.55202247441602</v>
+        <v>10.56502960583362</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>8.260130278303812</v>
+        <v>8.273109420702276</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5.645584495757582</v>
+        <v>5.658695300132521</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.558943388490547</v>
+        <v>4.571986284784913</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.820230432463944</v>
+        <v>4.83329668676442</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.276922466208397</v>
+        <v>2.290103475503635</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6.022150953728513</v>
+        <v>6.035349692683276</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>7.248150336174639</v>
+        <v>7.26155546382747</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>6.005334728120033</v>
+        <v>6.018792021830251</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5.693697124219796</v>
+        <v>5.707149412939906</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>6.311504797011914</v>
+        <v>6.325060843363516</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>6.561226129288201</v>
+        <v>6.550796493590049</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>395</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6.493903451941925</v>
+        <v>6.357467807849481</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>7.66713996555994</v>
+        <v>7.680049775135991</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>9.297587714659556</v>
+        <v>9.310594846077159</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>8.415182619418957</v>
+        <v>8.428161761817421</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>6.104609505612615</v>
+        <v>6.117720309987554</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>5.389393215480169</v>
+        <v>5.402436111774534</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>6.317317726055997</v>
+        <v>6.330383980356473</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.318488757654237</v>
+        <v>3.331669766949474</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>6.801792668940287</v>
+        <v>6.81499140789505</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>7.217490268722493</v>
+        <v>7.230895396375324</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>6.50640783048086</v>
+        <v>6.519865124191078</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>5.274968203016158</v>
+        <v>5.288420491736268</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>5.107878149033283</v>
+        <v>5.121434195384886</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>5.104434924347544</v>
+        <v>5.094005288649392</v>
       </c>
     </row>
     <row r="12">
@@ -4223,46 +4223,46 @@
         <v>501</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.881063671821906</v>
+        <v>3.781509416781745</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5.176425192574271</v>
+        <v>5.071244489947638</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7.176766066816</v>
+        <v>7.189773198233603</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6.109414409004344</v>
+        <v>6.122393551402808</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.972190798722586</v>
+        <v>4.985301603097525</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.670830341228672</v>
+        <v>4.683873237523038</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>5.184899019165968</v>
+        <v>5.197965273466444</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3.120909233158919</v>
+        <v>3.134090242454157</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>4.856316532605362</v>
+        <v>4.869515271560125</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>5.203796137996598</v>
+        <v>5.217201265649429</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>4.599841216872633</v>
+        <v>4.613298510582851</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3.835821180605286</v>
+        <v>3.849273469325396</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.415566569660385</v>
+        <v>3.429122616011988</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.064489498743065</v>
+        <v>4.054059863044913</v>
       </c>
     </row>
     <row r="13">
@@ -4275,46 +4275,46 @@
         <v>635</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.294630753573387</v>
+        <v>2.221278326832419</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5.1717176265742</v>
+        <v>5.091571345789575</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.972560305111067</v>
+        <v>5.890484982212818</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.898089028269744</v>
+        <v>3.911068170668209</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3.989589073040101</v>
+        <v>4.00269987741504</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.287031010755761</v>
+        <v>4.300073907050127</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>4.989698868286631</v>
+        <v>5.002765122587107</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.947712319898834</v>
+        <v>2.960893329194072</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>4.461515583322829</v>
+        <v>4.474714322277592</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.556272288058686</v>
+        <v>4.569677415711517</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>3.879078018859211</v>
+        <v>3.892535312569429</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3.59850054628339</v>
+        <v>3.6119528350035</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>3.178245935338488</v>
+        <v>3.191801981690091</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>3.427967267614775</v>
+        <v>3.417537631916623</v>
       </c>
     </row>
     <row r="14">
@@ -4327,46 +4327,46 @@
         <v>776</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.51941515022704</v>
+        <v>2.461317602328293</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>4.968347140184846</v>
+        <v>4.905327182314416</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.907335855074535</v>
+        <v>4.843885822406108</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.104599296960387</v>
+        <v>3.117578439358851</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.597105916939768</v>
+        <v>3.610216721314707</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.4100117721812</v>
+        <v>4.423054668475565</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4.969607951816137</v>
+        <v>4.982674206116613</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.827166821075878</v>
+        <v>2.840347830371115</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.31255868747089</v>
+        <v>4.325757426425653</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2.946969584917191</v>
+        <v>2.960374712570022</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.871082239981057</v>
+        <v>2.884539533691274</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.132269521037827</v>
+        <v>2.145721809757937</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.742942745144468</v>
+        <v>2.756498791496071</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.477200159894984</v>
+        <v>2.466770524196832</v>
       </c>
     </row>
     <row r="15">
@@ -4379,46 +4379,46 @@
         <v>958</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.512805176147992</v>
+        <v>1.469187919569592</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.707488066825768</v>
+        <v>3.660239187536057</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.477178797142628</v>
+        <v>3.429793158313451</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.206572910373218</v>
+        <v>2.160557057550051</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.50322476419457</v>
+        <v>2.516335568569509</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.905050835521919</v>
+        <v>2.918093731816285</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3.029085385473032</v>
+        <v>3.042151639773508</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.831213051409691</v>
+        <v>1.844394060704929</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.709670367732606</v>
+        <v>2.722869106687369</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.485849984374823</v>
+        <v>2.499255112027654</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.6547918583871</v>
+        <v>1.668249152097317</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.167254347674074</v>
+        <v>1.180706636394184</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.8513838703408609</v>
+        <v>0.8649399166924638</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.205489336228837</v>
+        <v>1.195059700530685</v>
       </c>
     </row>
     <row r="16">
@@ -4431,46 +4431,46 @@
         <v>1147</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.115257331963939</v>
+        <v>2.080335055477811</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3.597337936277462</v>
+        <v>3.560071789445303</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.078516572772727</v>
+        <v>3.041411957269055</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.171784872958739</v>
+        <v>3.134640833841416</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.807731574189965</v>
+        <v>2.820842378564905</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.802645177119224</v>
+        <v>3.81568807341359</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3.892279376150341</v>
+        <v>3.905345630450817</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.814808270306948</v>
+        <v>2.827989279602185</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.015360258579747</v>
+        <v>3.02855899753451</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.426786948006921</v>
+        <v>2.440192075659752</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.524561958475743</v>
+        <v>1.538019252185961</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.8614734506075692</v>
+        <v>0.8749257393276793</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.4412188396626675</v>
+        <v>0.4547748860142704</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.039676004545754</v>
+        <v>1.029246368847602</v>
       </c>
     </row>
     <row r="17">
@@ -4483,46 +4483,46 @@
         <v>1340</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.077990251218594</v>
+        <v>1.050682482476795</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.037951581345496</v>
+        <v>2.009088352592293</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.430074650840197</v>
+        <v>2.40069164429012</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.975637220651734</v>
+        <v>2.945885167276877</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.256130382242119</v>
+        <v>2.22661316342208</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.62819918562942</v>
+        <v>2.641242081923785</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.513614722088491</v>
+        <v>3.526680976388967</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.449416397933845</v>
+        <v>2.462597407229083</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.164535914736618</v>
+        <v>2.177734653691381</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.389037595380337</v>
+        <v>1.402442723033168</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.5872693456896272</v>
+        <v>0.6007266393998449</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.1738913090052137</v>
+        <v>0.1873435977253237</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.1267710264185169</v>
+        <v>0.1403270727701198</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.6003729557097301</v>
+        <v>0.589943320011578</v>
       </c>
     </row>
     <row r="18">
@@ -4535,46 +4535,46 @@
         <v>1561</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.244580849119103</v>
+        <v>1.222787673169357</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.45764791337308</v>
+        <v>1.43505442592258</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.569857044170313</v>
+        <v>2.546374573488215</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.864687473630532</v>
+        <v>2.841048372279289</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.555115915817041</v>
+        <v>2.531438522600396</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.852557853532701</v>
+        <v>2.865600749827067</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.53656212472935</v>
+        <v>3.549628379029826</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.813132729791533</v>
+        <v>2.826313739086771</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.303702350335691</v>
+        <v>2.316901089290454</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.453577165307763</v>
+        <v>1.466982292960594</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.09571685828679222</v>
+        <v>0.10917415199701</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.3823919766803954</v>
+        <v>-0.3689396879602853</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.2901545953126785</v>
+        <v>-0.2765985489610756</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.4079972302371573</v>
+        <v>0.3975675945390051</v>
       </c>
     </row>
     <row r="19">
@@ -4587,46 +4587,46 @@
         <v>1765</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.322276773063052</v>
+        <v>1.304394703928921</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.324852320219435</v>
+        <v>1.306428119477005</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.489366672057137</v>
+        <v>2.470140066307408</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.651890046630562</v>
+        <v>2.632598947063101</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.862489521390579</v>
+        <v>1.843453928119068</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.499874801882427</v>
+        <v>2.512917698176793</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.981713322570492</v>
+        <v>2.994779576870968</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.741158818973133</v>
+        <v>2.754339828268371</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.056929471034451</v>
+        <v>2.070128209989214</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.263461509802568</v>
+        <v>1.276866637455399</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.03887815715636833</v>
+        <v>0.05233545086658609</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.4933109234585373</v>
+        <v>-0.4798586347384273</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.06370717746292343</v>
+        <v>-0.05015113111132052</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.6392719451816262</v>
+        <v>0.6288423094834741</v>
       </c>
     </row>
     <row r="20">
@@ -4639,46 +4639,46 @@
         <v>2018</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.7443273743031185</v>
+        <v>0.7305464200585305</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.6427625475379344</v>
+        <v>0.6286096905392426</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.858357856023346</v>
+        <v>1.843492465929671</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.115521007688159</v>
+        <v>2.100551041469679</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.357429237150342</v>
+        <v>1.342685844515692</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.930523046996527</v>
+        <v>1.91556142133372</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.093559399099867</v>
+        <v>2.106625653400343</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.973254097444233</v>
+        <v>1.986435106739471</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.8716199198843242</v>
+        <v>0.8848186588390874</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.02149473485639675</v>
+        <v>0.03489986250922783</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.7283527420875373</v>
+        <v>-0.7148954483773196</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.9912936679928563</v>
+        <v>-0.9778413792727463</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.7177920846860175</v>
+        <v>-0.7042360383344146</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.4680707524097301</v>
+        <v>-0.4785003881078822</v>
       </c>
     </row>
     <row r="21">
@@ -4691,46 +4691,46 @@
         <v>2259</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.7309433052317189</v>
+        <v>0.7199669716731592</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.3359955789777729</v>
+        <v>0.3248590071438642</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.733541110892304</v>
+        <v>1.721699182764766</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.109806371651366</v>
+        <v>2.097816710389864</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.640623844136194</v>
+        <v>1.628724178556965</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.095900519597038</v>
+        <v>2.083852040978073</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.32103842693742</v>
+        <v>2.334104681237896</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.340796152547242</v>
+        <v>2.353977161842479</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.438716142416283</v>
+        <v>1.451914881371046</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.8099278321116898</v>
+        <v>0.8233329597645209</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.1182333834027816</v>
+        <v>0.1316906771129993</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.1129877089197819</v>
+        <v>-0.09953542019967188</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.04630119547335454</v>
+        <v>-0.03274514912175164</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.1148853869135991</v>
+        <v>0.1044557512154469</v>
       </c>
     </row>
     <row r="22">
@@ -4743,46 +4743,46 @@
         <v>2498</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.5229420233777233</v>
+        <v>0.5142916371972746</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.4913110084724508</v>
+        <v>0.4824084636970625</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.877568380621021</v>
+        <v>1.868042558793071</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.470372492836681</v>
+        <v>2.460624725998841</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.994712382206288</v>
+        <v>1.985062082139443</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.074741494103066</v>
+        <v>2.06510117780094</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.310263981794762</v>
+        <v>2.323330236095238</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.083272736736234</v>
+        <v>2.096453746031472</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.54188854310798</v>
+        <v>1.555087282062743</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.092083614285009</v>
+        <v>1.10548874193784</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.3669139569009801</v>
+        <v>0.3803712506111978</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.03905516757904337</v>
+        <v>-0.02560287885893331</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.06110655454251201</v>
+        <v>0.07466260089411492</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.03060370747531493</v>
+        <v>0.02017407177716279</v>
       </c>
     </row>
     <row r="23">
@@ -4795,98 +4795,98 @@
         <v>2696</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.3018226942291236</v>
+        <v>0.2948056571044333</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.1912843631220653</v>
+        <v>0.1840918786232209</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.11330943062562</v>
+        <v>1.105719084239375</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.74601370855202</v>
+        <v>1.738201579659005</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.413790358224276</v>
+        <v>1.406025758937083</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.435387280762072</v>
+        <v>1.427649311626219</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.684481456664869</v>
+        <v>1.697547710965345</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.551125951058431</v>
+        <v>1.564306960353669</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.8966542547871086</v>
+        <v>0.9098529937418718</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.640000879848202</v>
+        <v>0.6534060075010331</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.1385116504861159</v>
+        <v>0.1519689441963337</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.3093010378657723</v>
+        <v>-0.2958487491456623</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.2473598031133548</v>
+        <v>-0.2338037567617519</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.2943743758815813</v>
+        <v>-0.3048040115797335</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 9.131</t>
+          <t>X &lt; 9.13</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>2925</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.4075855705750087</v>
+        <v>0.402059063290281</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.2821509210422235</v>
+        <v>0.2764985589956765</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.169518267333004</v>
+        <v>1.16351911711623</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.694602079444131</v>
+        <v>1.688433602448256</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.4487523714077</v>
+        <v>1.442609058565829</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.218453044539991</v>
+        <v>1.212415605964551</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.543975737524129</v>
+        <v>1.557041991824605</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.350296612246908</v>
+        <v>1.363477621542145</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.9474163841842653</v>
+        <v>0.9606151231390285</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.8836159854811143</v>
+        <v>0.8970211131339454</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.57629855859944</v>
+        <v>0.5897558523096578</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.1320492373123869</v>
+        <v>0.145501526032497</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.01948693405979895</v>
+        <v>0.03304298041140186</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.07267207554425426</v>
+        <v>-0.0831017112424064</v>
       </c>
     </row>
     <row r="25">
@@ -4899,46 +4899,46 @@
         <v>3133</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.5021002393821163</v>
+        <v>0.4977395922754582</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.2144015191687672</v>
+        <v>0.2100011268798241</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.016700992882242</v>
+        <v>1.012010775994888</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.643131663490578</v>
+        <v>1.638249594418816</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.314031686188244</v>
+        <v>1.309208812601973</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.342154147494213</v>
+        <v>1.337343578271017</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.608521611198633</v>
+        <v>1.621587865499109</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.141338212417132</v>
+        <v>1.15451922171237</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.9526651695160311</v>
+        <v>0.9658639084707943</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.9324155031602999</v>
+        <v>0.9458206308131309</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.5361524437645215</v>
+        <v>0.5496097374747393</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.1236795525941545</v>
+        <v>0.1371318413142646</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.009310455733448464</v>
+        <v>0.004245590618154438</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.1106903044338594</v>
+        <v>-0.1211199401320115</v>
       </c>
     </row>
     <row r="26">
@@ -4951,46 +4951,46 @@
         <v>3311</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.4317727774981037</v>
+        <v>0.4283393206866322</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.3746260758755398</v>
+        <v>0.371106561564666</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.082497151418075</v>
+        <v>1.078737351375288</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.138974967934779</v>
+        <v>1.135204381161515</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.9796324371847973</v>
+        <v>0.9758740350522146</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.8107160786635035</v>
+        <v>0.8070254837552042</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.17901769814749</v>
+        <v>1.192083952447966</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.9534531456359971</v>
+        <v>0.9666341549312349</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.6206320573999307</v>
+        <v>0.6338307963546939</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.8275893248032915</v>
+        <v>0.8409944524561226</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.4416218657832118</v>
+        <v>0.4550791594934296</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.08337439793987045</v>
+        <v>0.09682668665998051</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.1161551237512342</v>
+        <v>0.1297111701028371</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.00344818662251356</v>
+        <v>-0.006981449075638579</v>
       </c>
     </row>
     <row r="27">
@@ -5003,46 +5003,46 @@
         <v>3475</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.2364467372612822</v>
+        <v>0.2338211139643462</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.3646632608470384</v>
+        <v>0.3619208649075674</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.020533391281511</v>
+        <v>1.017581794894838</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.022952303017867</v>
+        <v>1.020004884228818</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.759385109755307</v>
+        <v>0.7564857232093303</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.5836378197967136</v>
+        <v>0.5808020496341442</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.8442278435316339</v>
+        <v>0.85729409783211</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.751145164174595</v>
+        <v>0.7643261734698328</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.6038143427404918</v>
+        <v>0.617013081695255</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.6745524670650838</v>
+        <v>0.6879575947179148</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.3546912290784405</v>
+        <v>0.3681485227886583</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.2164125159202683</v>
+        <v>0.2298648046403784</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.1990356028170979</v>
+        <v>0.2125916491687008</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.3048720430070517</v>
+        <v>0.2944424073088996</v>
       </c>
     </row>
     <row r="28">
@@ -5052,101 +5052,101 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3613</v>
+        <v>3614</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.3664677311854376</v>
+        <v>0.3643878368689641</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.6213562260297394</v>
+        <v>0.6191440770097216</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.9604455974423445</v>
+        <v>0.9581237276887933</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.8847972715977335</v>
+        <v>0.8825001008143545</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.7489360633800004</v>
+        <v>0.7466550024934264</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.8127468402726379</v>
+        <v>0.8104582417883677</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.9493744954408712</v>
+        <v>0.9624407497413472</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.8142331553201316</v>
+        <v>0.8274141646153694</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.7532332691378301</v>
+        <v>0.7664320080925933</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.7608834023168782</v>
+        <v>0.7742885299697093</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.5284599064442403</v>
+        <v>0.5419172001544581</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.3968220344592837</v>
+        <v>0.4102743231793937</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.3639498252852817</v>
+        <v>0.3775058716368846</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.380354861844701</v>
+        <v>0.3818801494229049</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 21.36</t>
+          <t>X &lt; 21.35</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3740</v>
+        <v>3741</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.4022115330059322</v>
+        <v>0.4006207891027884</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.4598572606324964</v>
+        <v>0.4582047885982377</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.6937108155028682</v>
+        <v>0.6919839395912533</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.7585776210418089</v>
+        <v>0.7568362814300613</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.6089162791003346</v>
+        <v>0.607198834276204</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.7875760054320722</v>
+        <v>0.7858184254266831</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.6641890357647</v>
+        <v>0.6624611881043023</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.5979679465260901</v>
+        <v>0.6111489558213279</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.4835064190714107</v>
+        <v>0.4967051580261739</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.4353058531292859</v>
+        <v>0.448710980782117</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.2305525288117067</v>
+        <v>0.2440098225219245</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.1580124036123607</v>
+        <v>0.1714646923324707</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.1387201022103639</v>
+        <v>0.1522761485619668</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.2164636253561412</v>
+        <v>0.2176268749713444</v>
       </c>
     </row>
     <row r="30">
@@ -5156,101 +5156,101 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3836</v>
+        <v>3837</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.277834123193621</v>
+        <v>0.2766281942315203</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.5019636004020285</v>
+        <v>0.5006639445777239</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.7982188134965611</v>
+        <v>0.7968328945619234</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.7084974928366776</v>
+        <v>0.7071371077683395</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.6272469276733403</v>
+        <v>0.6258954154727761</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.7828272957302929</v>
+        <v>0.7814410609800575</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.6604061752993644</v>
+        <v>0.659049358553176</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.5841531909041038</v>
+        <v>0.5973342001993416</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.5231533047218022</v>
+        <v>0.5363520436765654</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.4288269208406064</v>
+        <v>0.4422320484934374</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.3283217070260207</v>
+        <v>0.3417790007362385</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.2584567538684581</v>
+        <v>0.2719090425885682</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.203070529684048</v>
+        <v>0.2166265760356509</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.3372724000936458</v>
+        <v>0.3381141157591898</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 26.25</t>
+          <t>X &lt; 26.24</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3914</v>
+        <v>3915</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.2092643824927194</v>
+        <v>0.2083523864934378</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.4218944682539743</v>
+        <v>0.4209014460091609</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.6276703806373405</v>
+        <v>0.6266179479079312</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.5933732583380831</v>
+        <v>0.5923312270718739</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.6049681230937622</v>
+        <v>0.6039138300343225</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.7378741958222648</v>
+        <v>0.7367903741532942</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.6162018884019673</v>
+        <v>0.6151472485512528</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.532062411990232</v>
+        <v>0.5452434212854698</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.5732075717731959</v>
+        <v>0.5864063107279591</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.4125614470108516</v>
+        <v>0.4259665746636827</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.3865619531324853</v>
+        <v>0.4000192468427031</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.3188000645126579</v>
+        <v>0.3322523532327679</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.2961349348457247</v>
+        <v>0.2951454222891243</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.4326627077670153</v>
+        <v>0.4332554947699663</v>
       </c>
     </row>
     <row r="32">
@@ -5260,101 +5260,101 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3979</v>
+        <v>3980</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.2028245340664228</v>
+        <v>0.2021331169079801</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.3104421561383646</v>
+        <v>0.3097037454763125</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.5565810917222791</v>
+        <v>0.5557757641003747</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.4496496012704156</v>
+        <v>0.4488723378700215</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.5777659902927539</v>
+        <v>0.5769496323402521</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.7133510256258191</v>
+        <v>0.7125038998739583</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.5922756750478797</v>
+        <v>0.5914575455771782</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.5521206610943139</v>
+        <v>0.5653016703895517</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.5162400916665959</v>
+        <v>0.5294388306213591</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.4448137260307803</v>
+        <v>0.4582188536836114</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.4410149357498767</v>
+        <v>0.4544722294600945</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.3246821925677992</v>
+        <v>0.3381344812879092</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.3457765015553917</v>
+        <v>0.3450120128024352</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.459033910798567</v>
+        <v>0.4594400574300153</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 31.14</t>
+          <t>X &lt; 31.13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4020</v>
+        <v>4021</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.2374454930968781</v>
+        <v>0.2368799486167958</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.4020652955320045</v>
+        <v>0.4014430601158168</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.492667795400564</v>
+        <v>0.4920189674352144</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.4129811884888497</v>
+        <v>0.4123531255481012</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.4845954129533681</v>
+        <v>0.48394406971709</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.6466639089924726</v>
+        <v>0.6459748791701614</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.5010791899035638</v>
+        <v>0.5004252305098618</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.5062975812762147</v>
+        <v>0.5194785905714525</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.3955711908671589</v>
+        <v>0.4087699298219221</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.2913435692405244</v>
+        <v>0.3047486968933555</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.2854962618299624</v>
+        <v>0.2989535555401801</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.1458366543817533</v>
+        <v>0.1592889431018634</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.2121251560439532</v>
+        <v>0.2115398799426131</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.2023630054609669</v>
+        <v>0.2027224979839417</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4057</v>
+        <v>4058</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.2494891090643137</v>
+        <v>0.2490396999132685</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.3241219250934861</v>
+        <v>0.3236420338433916</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.3856719076079571</v>
+        <v>0.3851737357412688</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.3571080910641484</v>
+        <v>0.3566176947970447</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.3739015363215188</v>
+        <v>0.3734028009971482</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.4386542992240052</v>
+        <v>0.4381416030328467</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.3182096337092446</v>
+        <v>0.3177257525083732</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.3437584349770191</v>
+        <v>0.3569394442722569</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.3073951587971777</v>
+        <v>0.3205938977519409</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.2210048838456231</v>
+        <v>0.2344100114984542</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.1887078295452937</v>
+        <v>0.2021651232555115</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.09990793687840238</v>
+        <v>0.1133602255985124</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.1124635593183285</v>
+        <v>0.112031742326991</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.1296920982273662</v>
+        <v>0.1299711257831078</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4085</v>
+        <v>4086</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.206292928263025</v>
+        <v>0.2059427872477713</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.3426909016253745</v>
+        <v>0.3422980718574777</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.3766776589336445</v>
+        <v>0.3762740967298654</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3491988987046497</v>
+        <v>0.3488026252131391</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.3621884995791333</v>
+        <v>0.361785798520863</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.4285321587287001</v>
+        <v>0.4281147618112158</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.332797496739822</v>
+        <v>0.3324028562265653</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.3305027693554337</v>
+        <v>0.3436837786506715</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.2695028831731321</v>
+        <v>0.2827016221278953</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.2268159168875599</v>
+        <v>0.2402210445403909</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1688695414322225</v>
+        <v>0.1823268351424403</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.05644574991541162</v>
+        <v>0.06989803863552169</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1149724568580979</v>
+        <v>0.1146358567192252</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.08483558747135334</v>
+        <v>0.08505221021547271</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/rsi/rsi_divergence_7_14.xlsx
+++ b/workspaces/btc_daily_14days/rsi/rsi_divergence_7_14.xlsx
@@ -575,46 +575,46 @@
         <v>27</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10.44810671016702</v>
+        <v>10.41909892149291</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>19.9223508716062</v>
+        <v>19.92133025580916</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>23.22750793653673</v>
+        <v>23.22752705025607</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>19.66904492707636</v>
+        <v>19.66868191053157</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4.354534570248738</v>
+        <v>4.402997426860466</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>8.34899616380131</v>
+        <v>8.372949497455068</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>8.266566496859163</v>
+        <v>8.314531412213867</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>7.802291482191393</v>
+        <v>7.851494750845738</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>7.743121326129184</v>
+        <v>7.81631191796918</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>14.29599532994099</v>
+        <v>14.39528092631096</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>10.39399629534613</v>
+        <v>10.49384986950498</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>10.43097924405583</v>
+        <v>10.55462736100572</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>10.01346394241637</v>
+        <v>10.16212280868518</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>13.9453883172493</v>
+        <v>14.11738707681427</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>43</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10.27580753325392</v>
+        <v>10.24680309852292</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>10.99023820996416</v>
+        <v>10.98915044646628</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>10.59953452501713</v>
+        <v>10.59946519266632</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>13.05248301703464</v>
+        <v>13.05207958248677</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>10.19827123342554</v>
+        <v>10.24676889534744</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.855835862020385</v>
+        <v>5.879776333273554</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5.772825430557461</v>
+        <v>5.820778324259379</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.30797830062069</v>
+        <v>5.357171149938821</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>9.893590634687172</v>
+        <v>9.966787846471981</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6.72362761706421</v>
+        <v>6.822892181183626</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>8.84463271114646</v>
+        <v>8.944482539596237</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>4.232430267045231</v>
+        <v>4.356069335588217</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>10.78842116427941</v>
+        <v>10.93708014355852</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>4.040134225948073</v>
+        <v>4.212132985513669</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>63</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.063501968749819</v>
+        <v>3.034439397569443</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3.040069706560899</v>
+        <v>3.038920172416518</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>8.979032016647544</v>
+        <v>8.97895464055599</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10.69508001911033</v>
+        <v>10.69466490299862</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3.826057811101471</v>
+        <v>3.874515631434413</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.708164555525052</v>
+        <v>5.732104616746021</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7.209654550793168</v>
+        <v>7.25761368511877</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.990551555803954</v>
+        <v>2.03972953604449</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8.271097940571636</v>
+        <v>8.344288769689889</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>10.59549047202124</v>
+        <v>10.69476421979716</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.463181573574857</v>
+        <v>2.563016881274407</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>5.671290089594429</v>
+        <v>5.794929800213033</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.094946845920866</v>
+        <v>-0.9462968429416279</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>3.892478264336837</v>
+        <v>4.064477023904942</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>72</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.67886918308897</v>
+        <v>1.649799219087946</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.226500570004212</v>
+        <v>4.225363738517963</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>7.988867514257599</v>
+        <v>7.988787411894045</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>6.736077616938665</v>
+        <v>6.735639136331258</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.429833295463126</v>
+        <v>3.478286366536729</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.341688415784049</v>
+        <v>2.365609406653341</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.644218132499212</v>
+        <v>3.692158518183064</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.179084721789671</v>
+        <v>3.228265779266096</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.731544243956058</v>
+        <v>1.804709978840584</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.8829107811309314</v>
+        <v>0.982154716310788</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.06659235498514</v>
+        <v>2.166424470836951</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>6.266120075888217</v>
+        <v>6.389758965292657</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>4.459183254436958</v>
+        <v>4.607835917254832</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.2972401691001</v>
+        <v>3.469238928665497</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>106</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>8.320819318972838</v>
+        <v>8.291500546130216</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.561332384116483</v>
+        <v>1.057729671982955</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.8712593183987</v>
+        <v>5.366968564709659</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>8.826101793727759</v>
+        <v>8.321467249453306</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>7.350886042902204</v>
+        <v>6.888173073607824</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>7.649885689486077</v>
+        <v>7.164118121350633</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>10.39237169908509</v>
+        <v>9.930605256017529</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>6.161527888671259</v>
+        <v>5.693744210543862</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>8.928376739595137</v>
+        <v>8.487304025381682</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>7.139314513727747</v>
+        <v>6.716816603841636</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>7.879491971573415</v>
+        <v>8.397707584943689</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.144447695784393</v>
+        <v>4.685927735362647</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.839275979465391</v>
+        <v>1.987925051246741</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.122187758197143</v>
+        <v>1.294186517764238</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>106</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-5.78461884129355</v>
+        <v>-6.303386809082262</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-4.584260800225849</v>
+        <v>-5.090531486789473</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.7138569416893219</v>
+        <v>-1.722953609753198</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.46527062037611</v>
+        <v>-3.476294888013925</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.7622359651969219</v>
+        <v>-0.2113505921163892</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.000876067745381</v>
+        <v>1.006616471226991</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.9752611583138133</v>
+        <v>0.004195118607285053</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.393541379409363</v>
+        <v>2.352782744667557</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.377657739578893</v>
+        <v>-2.392366715787084</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.284821626943035</v>
+        <v>-2.288071871771706</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.489752880063861</v>
+        <v>-2.497437626724995</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.512977169953267</v>
+        <v>-1.91521761433804</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.876451225764853</v>
+        <v>-3.257762867164601</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.1787915317837587</v>
+        <v>0.3507902913500018</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.606264728070578</v>
+        <v>-3.612398088829863</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5.193636254728432</v>
+        <v>5.151507098721986</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.077810852616572</v>
+        <v>1.064175121383997</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.346422283798823</v>
+        <v>-4.719546497366011</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.3266320086798871</v>
+        <v>-0.03243829948556964</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.85748510008743</v>
+        <v>2.459292650614017</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4.263394082936294</v>
+        <v>3.879289187399003</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.308910615375758</v>
+        <v>1.935058017217095</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.993669211911119</v>
+        <v>2.638936352745603</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.14565323952035</v>
+        <v>1.816213570477416</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.196325409522743</v>
+        <v>0.8720000706645124</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.722907018552334</v>
+        <v>2.411648289510879</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.303766604535539</v>
+        <v>2.01649036294689</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.037704514040911</v>
+        <v>0.7840537434811168</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>141</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.535867081785184</v>
+        <v>3.13917396074892</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.049654566399219</v>
+        <v>4.381580730536214</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.1197984227963076</v>
+        <v>-0.2582893912680007</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.4563617605967139</v>
+        <v>-0.1296359390543103</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.83614382904458</v>
+        <v>2.211329237371217</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.963675041248237</v>
+        <v>5.320216850446776</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>4.880588085523343</v>
+        <v>5.261551308869436</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.292701535786115</v>
+        <v>2.666005945481658</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.648593408215532</v>
+        <v>3.725623378421211</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-4.282912924366023</v>
+        <v>-4.186802665993561</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.654023816133126</v>
+        <v>-1.555107888358343</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-4.455173116044584</v>
+        <v>-4.333820583617566</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.795736200026262</v>
+        <v>0.9447803550670031</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.815052975108415</v>
+        <v>-1.643054215542072</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.760038142543159</v>
+        <v>-2.777005089417592</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.634814295983588</v>
+        <v>-1.632617675816803</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.578444968820548</v>
+        <v>-2.57096049045456</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.901095567323239</v>
+        <v>-1.895623271614909</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.143678614541329</v>
+        <v>-2.384717196589783</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-3.492130974935641</v>
+        <v>-3.750298296001375</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-5.222447296850397</v>
+        <v>-5.449719065133422</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.398557142138699</v>
+        <v>-2.639747318677088</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-4.106300662664204</v>
+        <v>-4.315209798429784</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.5318698797174477</v>
+        <v>0.3230035911445412</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.514859498933255</v>
+        <v>-3.706020572929901</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.932233134623814</v>
+        <v>-3.10140574813331</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-7.198065964515969</v>
+        <v>-7.321700286719121</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-4.227179855320429</v>
+        <v>-4.340414987545159</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>189</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>5.174332863823786</v>
+        <v>4.87216041873149</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.038855188101991</v>
+        <v>2.759746935912155</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.062703515677505</v>
+        <v>1.30962872140433</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>8.051616738369518</v>
+        <v>7.77800588922446</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.349457191714237</v>
+        <v>4.119523554549509</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>8.341366053775033</v>
+        <v>8.624001066157682</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>8.259835656206754</v>
+        <v>8.566188955170439</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>7.797317254261472</v>
+        <v>8.099625973644223</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>4.569414542092417</v>
+        <v>4.890023218601996</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.137234835801593</v>
+        <v>2.239244657836089</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.8767277299598106</v>
+        <v>0.9778201764846131</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.674676511260607</v>
+        <v>-0.5513146734521968</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.623748979740562</v>
+        <v>-1.475573129116434</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.1887745606338598</v>
+        <v>0.3607733202005221</v>
       </c>
     </row>
     <row r="16">
@@ -1092,517 +1092,517 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-5.068259927288096</v>
+        <v>-5.342982962615316</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-7.198903942440914</v>
+        <v>-7.445612546625988</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.394854812583006</v>
+        <v>-1.154184449163509</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.835709370913555</v>
+        <v>2.064498293471097</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.287486024607666</v>
+        <v>-1.00076770371345</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-4.32989610626916</v>
+        <v>-4.330874793245094</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.269922278874439</v>
+        <v>1.034227721466088</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.2885122164053158</v>
+        <v>0.05420494319997715</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.87532812686986</v>
+        <v>-3.07445985722233</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-4.759205733370862</v>
+        <v>-4.928479600186243</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-4.964749444196762</v>
+        <v>-5.134109131320983</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.896299784159936</v>
+        <v>-4.045014558904533</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.727817912123889</v>
+        <v>-1.862852897839382</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.020836975402666</v>
+        <v>-2.129271953349907</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -6.761</t>
+          <t>X ≈ -6.762</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>221</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.261771764094831</v>
+        <v>2.886045266275559</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.05203108619915</v>
+        <v>-1.875192773879043</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.417966519656943</v>
+        <v>3.606889563894462</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.193802118608914</v>
+        <v>2.838304631947473</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4.364832210228478</v>
+        <v>4.601782411085161</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.209697984462743</v>
+        <v>4.670330411719711</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.674938691268139</v>
+        <v>4.160058578760818</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>5.017789322658267</v>
+        <v>5.288463764477427</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.153070188863204</v>
+        <v>3.440578418279038</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.854756251002776</v>
+        <v>2.158832562742404</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.868064132105708</v>
+        <v>-2.771371808001483</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.738916059321184</v>
+        <v>-3.618182446202098</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.803432225197234</v>
+        <v>-2.655874309417612</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.7688734558376851</v>
+        <v>-0.5968746962709233</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -4.316</t>
+          <t>X ≈ -4.317</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>204</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.922042488960948</v>
+        <v>1.897379411143675</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.3163256586406433</v>
+        <v>0.3172925171420502</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.874679624599139</v>
+        <v>1.882805233525552</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.026879383027072</v>
+        <v>1.033943313165629</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.417533679339193</v>
+        <v>-3.375803762800778</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.190280835398184</v>
+        <v>-0.161841773393391</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.252805566574942</v>
+        <v>-1.202890019481593</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.194338698076884</v>
+        <v>2.252845847585931</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.1790283597248035</v>
+        <v>0.2550889247237578</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.1786827685508285</v>
+        <v>-0.07854357765996411</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.3819145872466692</v>
+        <v>-0.2826840251960547</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.3271281817267</v>
+        <v>-1.204909444693904</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.682078692266487</v>
+        <v>1.831305177761877</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.398547358641956</v>
+        <v>2.570546118208391</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -1.872</t>
+          <t>X ≈ -1.873</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.269921026963075</v>
+        <v>-3.293056834356086</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-4.094394337431915</v>
+        <v>-4.088587463439552</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.518931118612294</v>
+        <v>-2.51773161364423</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.60061786412863</v>
+        <v>-1.601312272471525</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.139681039393267</v>
+        <v>-2.090486486283758</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.235763685410873</v>
+        <v>-2.211401754866408</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-4.082472246836161</v>
+        <v>-4.24056178109965</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.366377341698353</v>
+        <v>-3.52529217927836</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-7.370057731212569</v>
+        <v>-7.49927266243099</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-8.6146574558692</v>
+        <v>-8.716802030647457</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-6.058562893622138</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-4.447211805448703</v>
+        <v>-4.532067079401251</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-5.264734131028227</v>
+        <v>-5.320925793366648</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-8.20363817960488</v>
+        <v>-8.221487230563881</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.5734</t>
+          <t>X ≈ 0.5719</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>241</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.6263549388419349</v>
+        <v>0.599392156000313</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.218124442042786</v>
+        <v>-2.223076546261176</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.6914018063355982</v>
+        <v>0.6973299298245266</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.060696092826312</v>
+        <v>2.072377715995522</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>4.00750982725117</v>
+        <v>4.074769827631449</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.475157069654351</v>
+        <v>3.517679827778096</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>4.217115691988639</v>
+        <v>4.286899257224732</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>5.409370668211366</v>
+        <v>5.480817534185881</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>6.1827659288316</v>
+        <v>6.273720443721189</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>7.410183948850431</v>
+        <v>7.524580659586796</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>7.210669145880871</v>
+        <v>7.320440212050705</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>7.248554541796352</v>
+        <v>7.378606949415513</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>5.587506653529047</v>
+        <v>5.738635744843378</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>4.985806328619887</v>
+        <v>5.157805088186649</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 3.018</t>
+          <t>X ≈ 3.016</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>239</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.432379442900164</v>
+        <v>-1.46241449843604</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.965977380944544</v>
+        <v>1.969992731602275</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.232164363219532</v>
+        <v>3.247468768235706</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>5.860166128326071</v>
+        <v>5.889030820578952</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>5.326466936969723</v>
+        <v>5.404654027009826</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.870618374699902</v>
+        <v>1.911749169259764</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.20191266748111</v>
+        <v>2.269503121875303</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.3455054234468449</v>
+        <v>-0.2883798477131592</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.518458212645932</v>
+        <v>2.60351783603722</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.76176385468915</v>
+        <v>3.871739464427158</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.726238243903794</v>
+        <v>2.83077893320911</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.6729021582507997</v>
+        <v>0.7968954613688837</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.089424388820731</v>
+        <v>1.238557618487114</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.7764464882691442</v>
+        <v>-0.6044477287025813</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 5.463</t>
+          <t>X ≈ 5.462</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>198</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.472700147897555</v>
+        <v>-2.505118750763835</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-3.57216516035318</v>
+        <v>-3.581703226986775</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-8.499333245745206</v>
+        <v>-8.519379907751841</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-7.368330444765846</v>
+        <v>-7.384767704531562</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-5.890049449295162</v>
+        <v>-5.856493008195734</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-6.599685815603117</v>
+        <v>-6.59380849947793</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-6.182874120982518</v>
+        <v>-6.149414083652829</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-5.13998185305423</v>
+        <v>-5.100095328884542</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-7.212718834991037</v>
+        <v>-7.157269958223473</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-5.039966244345052</v>
+        <v>-4.950795508735361</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.724470779558764</v>
+        <v>-2.629683431019046</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-3.699746033211078</v>
+        <v>-3.581617703754993</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.122492911506797</v>
+        <v>-3.976775630318926</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.40478003292079</v>
+        <v>-4.232781273353957</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 7.908</t>
+          <t>X ≈ 7.906</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>229</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.655297434603867</v>
+        <v>1.842122330665873</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.358590928942199</v>
+        <v>1.563006146463565</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.82429274604835</v>
+        <v>2.048302731495994</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.079212342178714</v>
+        <v>1.313356473200521</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.850077944732362</v>
+        <v>1.922166953870239</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.327908689808766</v>
+        <v>-1.298497308970127</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.1118308576082612</v>
+        <v>-0.04910973007336139</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.008278829927953</v>
+        <v>-0.9516237131642313</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.546853631662344</v>
+        <v>1.631491013943609</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.750408566593421</v>
+        <v>3.864430992080493</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>5.730217751445316</v>
+        <v>5.843696658081626</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>5.33440010797581</v>
+        <v>5.465182172739048</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.172722350425495</v>
+        <v>3.323299355345569</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.526983012379432</v>
+        <v>2.698981771946038</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 10.36</t>
+          <t>X ≈ 10.35</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.827390886150027</v>
+        <v>1.589189614198517</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.7237278053483678</v>
+        <v>-0.9517661691003312</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.130925548493479</v>
+        <v>-1.348022394784103</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.9007758500338099</v>
+        <v>0.715320910973027</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.5850101718208407</v>
+        <v>-0.7401118048580173</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.057236150413168</v>
+        <v>2.914316226038103</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.490673409991267</v>
+        <v>2.370568349373023</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.789957910473589</v>
+        <v>-1.959998710527167</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.025999227119165</v>
+        <v>0.9015794049737238</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.619434173167541</v>
+        <v>1.527026186477627</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.01755381463834027</v>
+        <v>-0.1263896233774062</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.01964728639472213</v>
+        <v>-0.06822288601245674</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.3999425189237016</v>
+        <v>-0.4633808125762826</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.6557512838919806</v>
+        <v>-0.6974277380004779</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 12.8</t>
+          <t>X ≈ 12.79</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.8010090010134547</v>
+        <v>-0.5574324834942104</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.183582549416855</v>
+        <v>3.44047336033951</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.213583580676634</v>
+        <v>2.4901737626288</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-7.701986340643543</v>
+        <v>-7.429768555466886</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-4.884374289606363</v>
+        <v>-4.567062389156298</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-8.489959772744918</v>
+        <v>-8.204891395477006</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-6.351226403267439</v>
+        <v>-6.030910613194081</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.345164789534046</v>
+        <v>-2.027469630560574</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-5.193766581822395</v>
+        <v>-4.857738329082899</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.010085984984457</v>
+        <v>-0.6536339490040319</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.208370003013449</v>
+        <v>-0.857774396540087</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.6108019359756369</v>
+        <v>-0.2409484412981371</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.335968259521145</v>
+        <v>2.715848939400615</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.001984239012074</v>
+        <v>2.406234583538811</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>164</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-3.679432319857881</v>
+        <v>-3.719933253458393</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.1654009966266443</v>
+        <v>0.1722402269297731</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2550320507708221</v>
+        <v>-0.2238520334800782</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.334404369010677</v>
+        <v>-1.308362369337978</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-3.671926405105538</v>
+        <v>-3.62687980297283</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-3.973518910329503</v>
+        <v>-3.963850381714842</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-5.881956976026217</v>
+        <v>-5.853774763623235</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-3.318803254687126</v>
+        <v>-3.27082703620173</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.2627058803624536</v>
+        <v>0.3507369400273319</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.402641167058341</v>
+        <v>-2.302359933470548</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.385534822300841</v>
+        <v>-1.286988185884681</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.908247776995374</v>
+        <v>3.039471234407031</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.883415448173409</v>
+        <v>2.034557210282195</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>6.379895995657733</v>
+        <v>6.551894755224396</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>139</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.574577428172098</v>
+        <v>3.580698338288791</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>6.955985402585874</v>
+        <v>7.028950024744404</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.5823764275340721</v>
+        <v>-0.5375270726167756</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-2.58334955113839</v>
+        <v>-2.558581706063677</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.4537557749382373</v>
+        <v>0.5492914551426296</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>6.443324324978718</v>
+        <v>6.577472657414837</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.502617650162591</v>
+        <v>3.639118726462719</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.344910576126637</v>
+        <v>2.453861505647716</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.441090510399775</v>
+        <v>4.57516227780588</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.892672956317611</v>
+        <v>3.031909236559251</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.854270647640242</v>
+        <v>4.986042170318086</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.901610935315304</v>
+        <v>5.044208907682979</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.491826764819947</v>
+        <v>4.649050981119188</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.567823702272975</v>
+        <v>2.020398001407941</v>
       </c>
     </row>
     <row r="28">
@@ -1716,49 +1716,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.402266051075287</v>
+        <v>1.765467961951984</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-4.086556117674149</v>
+        <v>-3.709435433907608</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-6.823881644901768</v>
+        <v>-6.431067596031966</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-2.808256017334166</v>
+        <v>-2.794642857142904</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-3.337671960951369</v>
+        <v>-3.283891998094781</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.06203276946913405</v>
+        <v>0.1138935207241261</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-7.791260155385977</v>
+        <v>-7.759262568501313</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-5.528782278189411</v>
+        <v>-5.881345328884635</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-7.14121247265561</v>
+        <v>-7.480817938021453</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-8.771028070111335</v>
+        <v>-9.085896518836478</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-8.192986754466403</v>
+        <v>-8.508786966372462</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-6.600770396307702</v>
+        <v>-6.888120229007633</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-6.245581804415949</v>
+        <v>-6.502028155571459</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-4.45647811611493</v>
+        <v>-4.690483293556113</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>96</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-4.543534978684576</v>
+        <v>-4.062808411398848</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.066510882946886</v>
+        <v>2.664251693205401</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.703002553476551</v>
+        <v>4.887973101642423</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.312852236091977</v>
+        <v>-1.232142857142861</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.251142015296402</v>
+        <v>1.403608001905219</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.4963181152095117</v>
+        <v>0.6347268540574831</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.4366739027196118</v>
+        <v>0.5740707648320225</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.01786166767906394</v>
+        <v>0.1082380044486442</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.005107167631031</v>
+        <v>2.15459872864519</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.1566799257147196</v>
+        <v>0.2891034811635649</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>4.107191569537321</v>
+        <v>4.251629700294117</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4.159958117953913</v>
+        <v>4.309796437659031</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>2.716169477054805</v>
+        <v>2.872971844428541</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>5.033351280210582</v>
+        <v>5.205350039777265</v>
       </c>
     </row>
     <row r="30">
@@ -1820,49 +1820,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.113587339500164</v>
+        <v>-3.142299974329639</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-3.465753011866923</v>
+        <v>-3.460377517637774</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-7.65655225041656</v>
+        <v>-7.651583860382821</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-5.004071467277775</v>
+        <v>-4.990054249547924</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.5041719385070564</v>
+        <v>-0.4160122512593247</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.476355324959876</v>
+        <v>-1.409049517250573</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.548421289757037</v>
+        <v>-1.469705606475983</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.00916773630928</v>
+        <v>-1.935538366859348</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2.994124101529913</v>
+        <v>3.090780163244403</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.3616208327788115</v>
+        <v>-0.2646939871908245</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.254622372161073</v>
+        <v>3.328633919703385</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>3.303913720301253</v>
+        <v>3.386800657068278</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>4.17073035214127</v>
+        <v>4.257465515314621</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>5.113479485338786</v>
+        <v>4.506510377329988</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>65</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.2494323439422885</v>
+        <v>0.5728208674207096</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-6.354545562512186</v>
+        <v>-6.400981217735144</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-3.846244787229139</v>
+        <v>-3.717796129126775</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-8.189306934265574</v>
+        <v>-8.203296703296708</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.227398027410445</v>
+        <v>-1.000238151940962</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.9816235849786352</v>
+        <v>-0.7274526331219846</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.004414439600886</v>
+        <v>-0.788108722347495</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.555428085938409</v>
+        <v>1.822981594192264</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.984801956136344</v>
+        <v>-2.829375630329139</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>2.294652878018255</v>
+        <v>2.500641942701961</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3.653567857298157</v>
+        <v>3.834963033627496</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.6734959722893521</v>
+        <v>0.8162066940693293</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>3.349282296650756</v>
+        <v>3.497971844428541</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>2.036556408415713</v>
+        <v>2.208555167982375</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>41</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.35904399393344</v>
+        <v>3.587449150722776</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>8.872376514476791</v>
+        <v>9.321345236298626</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-5.859740115860717</v>
+        <v>-5.706539093479492</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-3.284029019708768</v>
+        <v>-3.137630662020911</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-8.607320855889888</v>
+        <v>-8.504928583460632</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-6.041076910427385</v>
+        <v>-5.793118674397839</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-8.376995581847304</v>
+        <v>-8.292799153867165</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-4.112046753569551</v>
+        <v>-3.880583133762705</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-11.22173715677424</v>
+        <v>-11.23462891363121</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-14.43346858810231</v>
+        <v>-14.49748188469006</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-14.68825357801598</v>
+        <v>-14.70162233222615</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-17.11565145171611</v>
+        <v>-17.08247998510519</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-12.74827867895904</v>
+        <v>-12.59958913118121</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-24.71766497995202</v>
+        <v>-24.54566622038536</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>37</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.227364397544726</v>
+        <v>1.543942229167072</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-8.129960691658106</v>
+        <v>-8.147342964096886</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-11.25658665390527</v>
+        <v>-11.2437836551143</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-5.842422249867617</v>
+        <v>-5.708494208494209</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-11.60472776523429</v>
+        <v>-11.60314875485154</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-21.81530895831953</v>
+        <v>-22.14117404684342</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-19.10824144191522</v>
+        <v>-19.49912743336618</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-17.02322540274477</v>
+        <v>-17.26225749104682</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-9.191333082863245</v>
+        <v>-9.191121992075502</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-7.32835796938793</v>
+        <v>-7.312247870187804</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-10.20691009177366</v>
+        <v>-10.21909102042657</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-4.837449594849687</v>
+        <v>-4.755518877656286</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-10.70477175740332</v>
+        <v>-10.55608220962551</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-7.776333404474101</v>
+        <v>-7.604334644907439</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>28</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-6.211783377473118</v>
+        <v>-6.081540396315532</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.412999917218166</v>
+        <v>3.049568232814337</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-1.553200038965478</v>
+        <v>-0.915598326928972</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-1.316682378370302</v>
+        <v>-0.7857142857143131</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-1.854971931465997</v>
+        <v>-1.274963426666233</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1.663890418837724</v>
+        <v>-1.002177907847283</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1.929120310331491</v>
+        <v>2.508594574355826</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-2.003084387876996</v>
+        <v>-1.528666757456065</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-5.275450414131342</v>
+        <v>-5.137067938021431</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.9210675274242135</v>
+        <v>1.181960624020739</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-2.679763053294884</v>
+        <v>-2.593608394943978</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-6.13797425744329</v>
+        <v>-6.106870229007633</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.4921394395078309</v>
+        <v>0.6408289872856798</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
   </sheetData>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4081</v>
+        <v>4092</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.1360210622881368</v>
+        <v>-0.1349595715374079</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.2196369391369117</v>
+        <v>-0.2190199041948873</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1369223842085532</v>
+        <v>-0.1365516363541275</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.05547581025346915</v>
+        <v>0.0553388590931192</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.05386212323951867</v>
+        <v>-0.05487773328132306</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03682104696651578</v>
+        <v>0.03614961828512975</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.08778446092323833</v>
+        <v>0.08640100798075423</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.1479411801676775</v>
+        <v>0.1463663597439435</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.02707093849352304</v>
+        <v>0.02524595018943643</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.02597211830482138</v>
+        <v>-0.02827933133643512</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.04555225018747677</v>
+        <v>-0.04782084915640894</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.05157863122790474</v>
+        <v>0.04847906263868396</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.06081079497103303</v>
+        <v>-0.06420748613583527</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.09075024719282965</v>
+        <v>-0.09462552229509669</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4054</v>
+        <v>4065</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2065122931357735</v>
+        <v>-0.2050603290556907</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.3537843665888332</v>
+        <v>-0.3527934476930668</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.292531564933789</v>
+        <v>-0.2917373988482197</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.07515230177272514</v>
+        <v>-0.07493426818579962</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.08322243668899887</v>
+        <v>-0.08448723619001441</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.01853877744260046</v>
+        <v>-0.01922396024810524</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.03331304627837284</v>
+        <v>0.03174921931794472</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.09696252744083722</v>
+        <v>0.09518838519050377</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.02431864228254454</v>
+        <v>-0.02650282745634058</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.1213576933178047</v>
+        <v>-0.1240815765901857</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.115080570545004</v>
+        <v>-0.1178393262545328</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.01754909855659292</v>
+        <v>-0.02130347218442097</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1279063593295575</v>
+        <v>-0.1321314511936933</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1842321764577335</v>
+        <v>-0.1890226539496993</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4011</v>
+        <v>4022</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.3188881975323667</v>
+        <v>-0.3168032747011154</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.4753981713237536</v>
+        <v>-0.4740524202064478</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.4093001617594894</v>
+        <v>-0.4081774066640165</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.215887360039666</v>
+        <v>-0.2152777777777786</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1934453805471179</v>
+        <v>-0.19494074530391</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.08151511987513516</v>
+        <v>-0.0822913427994294</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02821750284255131</v>
+        <v>-0.03014243943702866</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.04109773605546252</v>
+        <v>0.03893148342915254</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.1306437729007541</v>
+        <v>-0.1333430808076415</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.1947394854759708</v>
+        <v>-0.1983530513749372</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.2111333431983837</v>
+        <v>-0.2147264073663138</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.06311108128431897</v>
+        <v>-0.06810283338138845</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.2449350513054185</v>
+        <v>-0.2504745885816462</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.2295195749377683</v>
+        <v>-0.2360762821189937</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3948</v>
+        <v>3959</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.3728625086964357</v>
+        <v>-0.3701319658738882</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.5314960629921188</v>
+        <v>-0.5299547372903817</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.5591139731170429</v>
+        <v>-0.5575558656119526</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.389998541621857</v>
+        <v>-0.3888888888888928</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2575863889244872</v>
+        <v>-0.2596984497076775</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1739036253336508</v>
+        <v>-0.1748164616302788</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1437154611452414</v>
+        <v>-0.1461132997166459</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.009989430421178724</v>
+        <v>0.007092565188486333</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.2647141193923446</v>
+        <v>-0.2682485636521292</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.3669240060743348</v>
+        <v>-0.3716964179028039</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.2538085812320006</v>
+        <v>-0.2589289401231554</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.1546174829472733</v>
+        <v>-0.1614019129258395</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.2313710333062389</v>
+        <v>-0.2394018929452031</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2952961362027935</v>
+        <v>-0.3045114572337937</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3876</v>
+        <v>3887</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.4109751717017431</v>
+        <v>-0.4075477223228887</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.6198799013759597</v>
+        <v>-0.6180388459238273</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.717900006938244</v>
+        <v>-0.7158621985114664</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.5223714733598186</v>
+        <v>-0.520858535870083</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3260833490059909</v>
+        <v>-0.3289381993268137</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2206328892553344</v>
+        <v>-0.2218734882617284</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.2140795526680463</v>
+        <v>-0.2172106938223237</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.04887921276213802</v>
+        <v>-0.05257413700179114</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.3017963180923076</v>
+        <v>-0.3066465608374855</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.3901407513475021</v>
+        <v>-0.3967741852460946</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.2969120041957822</v>
+        <v>-0.3038544470923199</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.2738881496748675</v>
+        <v>-0.2827509181308017</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.3185020727070409</v>
+        <v>-0.3291886493986169</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.3620305567347302</v>
+        <v>-0.3744137026119176</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3770</v>
+        <v>3781</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.6564845128188566</v>
+        <v>-0.6514247697854785</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.6812084165648713</v>
+        <v>-0.6650188678487439</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.9031654946002448</v>
+        <v>-0.8863938200140993</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.7852197933362888</v>
+        <v>-0.7687523558236009</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.5419344777970423</v>
+        <v>-0.5312692744209855</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.4419259845727339</v>
+        <v>-0.4289391086317096</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.5122980759268927</v>
+        <v>-0.5017038148704671</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.2234954336512516</v>
+        <v>-0.2136716627462505</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.5613184252845898</v>
+        <v>-0.5531841863702027</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.6018442680843705</v>
+        <v>-0.5962030727476346</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.5268055907824021</v>
+        <v>-0.5478019676942267</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.398117221191761</v>
+        <v>-0.4220473839521048</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.3791716943331167</v>
+        <v>-0.3941487266978498</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.4037618939715557</v>
+        <v>-0.4211927619506923</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3664</v>
+        <v>3675</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.5081269148880949</v>
+        <v>-0.48840219123705</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.5682925997886485</v>
+        <v>-0.5373714290439224</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.9086422158362097</v>
+        <v>-0.8622644764189076</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.7366157028160316</v>
+        <v>-0.6906572514937537</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.5796642995648824</v>
+        <v>-0.5404968609037937</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.5125965679640316</v>
+        <v>-0.470345609710634</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.5553333594502234</v>
+        <v>-0.5162957296864192</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.2992066514963483</v>
+        <v>-0.2876972864702978</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.5087714909736718</v>
+        <v>-0.5001356562700252</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.5531555126151986</v>
+        <v>-0.5474035917417694</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.4700172685488226</v>
+        <v>-0.4915675786174205</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.3658641768225692</v>
+        <v>-0.3789790725450501</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.3069250703342732</v>
+        <v>-0.3115519650952692</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.4206152408956854</v>
+        <v>-0.4434594840322816</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3530</v>
+        <v>3540</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.3905205503083593</v>
+        <v>-0.3692667544644479</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.7870173778354683</v>
+        <v>-0.7543201864587274</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.9840486495961613</v>
+        <v>-0.9357303932842669</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.5995862178722078</v>
+        <v>-0.5370131700833767</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.6140676155152534</v>
+        <v>-0.5598719755341435</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.6405260137200912</v>
+        <v>-0.5820691026891112</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.7382538912575356</v>
+        <v>-0.6839239680498466</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.3982116695589113</v>
+        <v>-0.3724633785600702</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.6417253306865831</v>
+        <v>-0.6198460294951929</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.6556032102883336</v>
+        <v>-0.637541534368772</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.533272203070517</v>
+        <v>-0.5435680398188509</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.483114981406203</v>
+        <v>-0.4854013024539583</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.4060278137995823</v>
+        <v>-0.4003332403172166</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.4759735545391806</v>
+        <v>-0.4902714291493169</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3389</v>
+        <v>3399</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.5538786666037794</v>
+        <v>-0.5148066605677357</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.988248048870318</v>
+        <v>-0.9673716808089026</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.029974420386175</v>
+        <v>-0.9638325354685264</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.6055450990984781</v>
+        <v>-0.5539123138242132</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.7160091362242937</v>
+        <v>-0.6748291308797434</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.873689881749165</v>
+        <v>-0.8269123858288978</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.9720268976683073</v>
+        <v>-0.9305588647976037</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.5101676335464163</v>
+        <v>-0.498507560581217</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.8202248710185955</v>
+        <v>-0.8001082202913707</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.5046882885754513</v>
+        <v>-0.4903082835423191</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.4866431155987527</v>
+        <v>-0.5016065456605503</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.3178567350255577</v>
+        <v>-0.3257581372159279</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.4560274378625593</v>
+        <v>-0.4561323038503673</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.4202608964393661</v>
+        <v>-0.4424507839944525</v>
       </c>
     </row>
     <row r="15">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3207</v>
+        <v>3216</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.428677224564197</v>
+        <v>-0.3860808171350456</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.9515548599165911</v>
+        <v>-0.9295171978840244</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.9420973889502378</v>
+        <v>-0.8723821574329449</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.5320214990932115</v>
+        <v>-0.4775649552185897</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.6349876691043335</v>
+        <v>-0.577531395797358</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.7250911043996453</v>
+        <v>-0.6605630010149852</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.7308118952825424</v>
+        <v>-0.6734051593680448</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.4029999096412737</v>
+        <v>-0.3766646265850895</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.6337372520352744</v>
+        <v>-0.6000884476547625</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.5635138534738928</v>
+        <v>-0.5365881570086444</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.3147892391513309</v>
+        <v>-0.319265822093918</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.1694886325226292</v>
+        <v>-0.1678155026394776</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.07341097018220211</v>
+        <v>-0.0654609913923494</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.2042149810928251</v>
+        <v>-0.2206449850983816</v>
       </c>
     </row>
     <row r="16">
@@ -2734,49 +2734,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3018</v>
+        <v>3027</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.7795615541550944</v>
+        <v>-0.7143951856777591</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.201451314215959</v>
+        <v>-1.159867683938685</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.06764655096967</v>
+        <v>-1.008622678113561</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.069565444381638</v>
+        <v>-0.993026762156056</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.9471348124756815</v>
+        <v>-0.8708063827863057</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.292871224643179</v>
+        <v>-1.240273145942517</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.293844495425517</v>
+        <v>-1.250307467808007</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.9165386584741384</v>
+        <v>-0.9059077463219083</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.9595807540532135</v>
+        <v>-0.9428803554587049</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.732646226659142</v>
+        <v>-0.7099057658641712</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.3894071010340383</v>
+        <v>-0.4002533522331149</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.1378516182477938</v>
+        <v>-0.1438705593677199</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.0236777918477955</v>
+        <v>0.0225836713198575</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.2288256581592094</v>
+        <v>-0.2569476146661032</v>
       </c>
     </row>
     <row r="17">
@@ -2786,465 +2786,465 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2825</v>
+        <v>2833</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.4865637537959131</v>
+        <v>-0.3974357685489593</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.7917138426239489</v>
+        <v>-0.7294283957772549</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.045292145839987</v>
+        <v>-0.9986548053342901</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.268049706099141</v>
+        <v>-1.202401933632117</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.9238824995760453</v>
+        <v>-0.8619068076857559</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.085385984942725</v>
+        <v>-1.028632934302316</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.46899741133344</v>
+        <v>-1.406749340988092</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.998866027979183</v>
+        <v>-0.9716549619121793</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.8286996061050331</v>
+        <v>-0.7969126804349997</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.4575573824837846</v>
+        <v>-0.4210235477708082</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.07682619051000472</v>
+        <v>-0.07608532500294984</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.1189202387508175</v>
+        <v>0.1232744939009507</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.1433374983492257</v>
+        <v>0.1516958119541343</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.1063979823262926</v>
+        <v>-0.1287333818017729</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -5.539</t>
+          <t>X &gt; -5.54</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2604</v>
+        <v>2612</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.7198134271652847</v>
+        <v>-0.6752494395658815</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.6847514344710746</v>
+        <v>-0.6324858507694131</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.424086372059186</v>
+        <v>-1.388327586957388</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.561855102896558</v>
+        <v>-1.544284074134829</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.372732711122424</v>
+        <v>-1.324186791356652</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.534776751931432</v>
+        <v>-1.510819342981819</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.905560344772368</v>
+        <v>-1.877754145836683</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.509496147983356</v>
+        <v>-1.501320443739175</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.166630145539742</v>
+        <v>-1.155444660839215</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.653802126339599</v>
+        <v>-0.6393038695255626</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.1600645871753557</v>
+        <v>0.1519615022339025</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.4463326127423315</v>
+        <v>0.439837274820853</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.3934281699712514</v>
+        <v>0.3892429010901068</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.05017406541153946</v>
+        <v>-0.08912418176436887</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -3.094</t>
+          <t>X &gt; -3.095</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2400</v>
+        <v>2408</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.9443711800360219</v>
+        <v>-0.8931964020014149</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.7698429873855588</v>
+        <v>-0.712948802203762</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.704481481775147</v>
+        <v>-1.66545013487206</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.78189753420007</v>
+        <v>-1.762705331198489</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.198924628824003</v>
+        <v>-1.150378709058231</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.649058904836764</v>
+        <v>-1.625101495887151</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.961044500919137</v>
+        <v>-1.934927020328558</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.824322109898489</v>
+        <v>-1.819364431874689</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.281011118487221</v>
+        <v>-1.274941692174281</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.6941872717516446</v>
+        <v>-0.686810140098892</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.2061328170012189</v>
+        <v>0.1887836316341165</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.5970767802721966</v>
+        <v>0.5791762826202742</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.2838928755761643</v>
+        <v>0.2670748344617664</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.2583153864560899</v>
+        <v>-0.3144450875760185</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.6492</t>
+          <t>X &gt; -0.6502</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2147</v>
+        <v>2154</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.6703310723170901</v>
+        <v>-0.6102045032929198</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.3780816964858289</v>
+        <v>-0.3148929897832105</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.608507677341144</v>
+        <v>-1.564948976279616</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.803259321125118</v>
+        <v>-1.781736824660264</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.088066980070387</v>
+        <v>-1.039521060304615</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.579922291196681</v>
+        <v>-1.555964882247068</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.711057905801759</v>
+        <v>-1.663046226811439</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.642608102611398</v>
+        <v>-1.618201178466826</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.5634848991022636</v>
+        <v>-0.5409676594699206</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.2391517858085521</v>
+        <v>0.2600876965767469</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.9443573231901894</v>
+        <v>0.9380271004798431</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.191489920555092</v>
+        <v>1.181894859200348</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.9377366728145944</v>
+        <v>0.9260126986532313</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.6779522738451007</v>
+        <v>0.6179544966017545</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 1.796</t>
+          <t>X &gt; 1.794</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1906</v>
+        <v>1913</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.8342876980722522</v>
+        <v>-0.7625896548296041</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.1454215172207611</v>
+        <v>-0.07449976599273356</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.899314700198488</v>
+        <v>-1.849951180341876</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.291828709772702</v>
+        <v>-2.267278698313184</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.732366041226996</v>
+        <v>-1.683820121461224</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.219100741335765</v>
+        <v>-2.195143332386152</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.460632846550702</v>
+        <v>-2.412621167560381</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.534280129772092</v>
+        <v>-2.512536520729924</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.4164998254045</v>
+        <v>-1.399482992909057</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.6675736870629478</v>
+        <v>-0.6550941142363342</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.1520272343819755</v>
+        <v>0.1339698292364631</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.4256176363372859</v>
+        <v>0.4012322278663873</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.3498066804996967</v>
+        <v>0.3197177932001054</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.1332550927324405</v>
+        <v>0.04602350205289696</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 4.241</t>
+          <t>X &gt; 4.239</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1667</v>
+        <v>1674</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.7485384917051974</v>
+        <v>-0.6626743993804212</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.448135576405825</v>
+        <v>-0.3663956482658506</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.635021656501372</v>
+        <v>-2.57771902246256</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.460591017094607</v>
+        <v>-3.431769722814508</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.744400283451952</v>
+        <v>-2.69585436368618</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.805449192884971</v>
+        <v>-2.781491783935358</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-3.129108178196539</v>
+        <v>-3.081096499206218</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.848087661152853</v>
+        <v>-2.830083381453349</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.980659976030807</v>
+        <v>-1.970998642919902</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.302613682551112</v>
+        <v>-1.301398310951129</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.2170408107744279</v>
+        <v>-0.2510584717488769</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.3901641265968365</v>
+        <v>0.3447426742181818</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.2437667091207416</v>
+        <v>0.1885333736997481</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.2636802144237294</v>
+        <v>0.1388924531583697</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 6.686</t>
+          <t>X &gt; 6.684</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1469</v>
+        <v>1476</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.5161463828378814</v>
+        <v>-0.4155172302923944</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.0270614731916794</v>
+        <v>0.06492610009915012</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.844597085588994</v>
+        <v>-1.780666952484736</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.933884137122575</v>
+        <v>-2.90148950575491</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.320412172603106</v>
+        <v>-2.271866252837334</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.294040852995117</v>
+        <v>-2.270083444045504</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.717504599795163</v>
+        <v>-2.669492920804842</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.539173399752947</v>
+        <v>-2.52556958362721</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.275453948750943</v>
+        <v>-1.275279320135276</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.798872493146618</v>
+        <v>-0.8118450283215353</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.1209245628261968</v>
+        <v>0.06802536425077932</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.9414249922482867</v>
+        <v>0.8714495541901925</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.8322754939296217</v>
+        <v>0.7472943376534715</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.8929212824796977</v>
+        <v>0.7253364896417338</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 9.13</t>
+          <t>X &gt; 9.128</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1240</v>
+        <v>1247</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.9171630233170376</v>
+        <v>-0.830111824886977</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.2829601829405988</v>
+        <v>-0.2101824248546862</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.522158191592993</v>
+        <v>-2.48382177015241</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-3.675012438541927</v>
+        <v>-3.67550693091993</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.090607524917488</v>
+        <v>-3.042061605151716</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.472463647648084</v>
+        <v>-2.448506238698471</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-3.1987137021829</v>
+        <v>-3.150702023192579</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.821895058212561</v>
+        <v>-2.814610164490105</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.796670429327257</v>
+        <v>-1.809080768815363</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.639021979179248</v>
+        <v>-1.670599806727367</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.9149852276526644</v>
+        <v>-0.9926231732690809</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.1301416845856949</v>
+        <v>0.02785310699878352</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.4000478083348327</v>
+        <v>0.2742348757036055</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.5911469791353099</v>
+        <v>0.3628948139018036</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 11.58</t>
+          <t>X &gt; 11.57</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1032</v>
+        <v>1040</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.47032892755071</v>
+        <v>-1.311645861320351</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.1941232978041469</v>
+        <v>-0.06257873729811791</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.802561670047155</v>
+        <v>-2.709889530442069</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-4.597264341665721</v>
+        <v>-4.549450549450555</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-3.595611642595877</v>
+        <v>-3.500238151940941</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-3.586976785241824</v>
+        <v>-3.515914171583546</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-4.345411879830415</v>
+        <v>-4.249647183885926</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-3.029882390314988</v>
+        <v>-2.984710713500036</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.36558059264204</v>
+        <v>-2.348606399559912</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.295765079652249</v>
+        <v>-2.307050364990282</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.095862876787336</v>
+        <v>-1.165036966372519</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.1524118733683721</v>
+        <v>0.0469759248385202</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.5612861688675537</v>
+        <v>0.4210487675054608</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.8424598073423653</v>
+        <v>0.5739397833669813</v>
       </c>
     </row>
     <row r="26">
@@ -3254,101 +3254,101 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.609835891161524</v>
+        <v>-1.46844515822032</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.8981416125645012</v>
+        <v>-0.790855538084557</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-3.848081406146491</v>
+        <v>-3.790971213902786</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-3.950144299724208</v>
+        <v>-3.950638792102211</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-3.326993666989473</v>
+        <v>-3.278447747223701</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-2.565043563022208</v>
+        <v>-2.541086154072595</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.927338126701848</v>
+        <v>-3.879326447711527</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-3.172598705231863</v>
+        <v>-3.183719022264448</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.776099203796491</v>
+        <v>-1.82696340840473</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.563740347627508</v>
+        <v>-2.650791989219712</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.072412913709755</v>
+        <v>-1.228916176593195</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.3114892247304795</v>
+        <v>0.1068347651851695</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.1913875598086037</v>
+        <v>-0.05603512421257051</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.6007790709990246</v>
+        <v>0.1930097378027966</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 16.47</t>
+          <t>X &gt; 16.46</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.117931812456874</v>
+        <v>-0.9386832534584144</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.150925653009942</v>
+        <v>-1.017466306323236</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-4.702081542786502</v>
+        <v>-4.630293374002243</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-4.57185639919814</v>
+        <v>-4.572350891576143</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-3.245009653872032</v>
+        <v>-3.19646373410626</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-2.230275509459325</v>
+        <v>-2.206318100509712</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-3.462762052369683</v>
+        <v>-3.414750373379363</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-3.137848638404812</v>
+        <v>-3.163223018985086</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.260684760031367</v>
+        <v>-2.339363490388742</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.602030587646851</v>
+        <v>-2.732776002337161</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.9979897354359366</v>
+        <v>-1.215252174406963</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.3057113587063967</v>
+        <v>-0.583197345219979</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.2107755904694031</v>
+        <v>-0.5479392029172274</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.7728081400792775</v>
+        <v>-1.303198501590529</v>
       </c>
     </row>
     <row r="28">
@@ -3358,49 +3358,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-2.301704561000307</v>
+        <v>-2.064479026313002</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-3.19604477592793</v>
+        <v>-3.021860338614268</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-5.74135379509157</v>
+        <v>-5.649817596031966</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-5.073494242901063</v>
+        <v>-5.073988735279066</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.178092039724355</v>
+        <v>-4.129546119958583</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-4.41835241869142</v>
+        <v>-4.394395009741807</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-5.219908656093786</v>
+        <v>-5.171896977103465</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-4.520976643522545</v>
+        <v>-4.562460920282504</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-3.951332242045751</v>
+        <v>-4.061799120817149</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-3.988171772058934</v>
+        <v>-4.168781823495941</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.474331283979652</v>
+        <v>-2.760019045225569</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.619355276798984</v>
+        <v>-1.985006429724478</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.39709451494349</v>
+        <v>-1.842529947686153</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.615544666552886</v>
+        <v>-2.131119494272937</v>
       </c>
     </row>
     <row r="29">
@@ -3410,49 +3410,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-3.411148588673889</v>
+        <v>-3.204556269331427</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.929311425923757</v>
+        <v>-2.817186821875787</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-5.417106066492757</v>
+        <v>-5.417259456497078</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-5.751997201974163</v>
+        <v>-5.752491694352166</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-4.429821638790784</v>
+        <v>-4.381275719025012</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-5.76035458589989</v>
+        <v>-5.736397176950277</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-4.449716107956746</v>
+        <v>-4.401704428966426</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-4.219110333138843</v>
+        <v>-4.169862770745127</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-2.99587283334894</v>
+        <v>-3.044044682207499</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.555570946934751</v>
+        <v>-2.705082565348064</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.7614321218291451</v>
+        <v>-1.048757896605089</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.12728046505935</v>
+        <v>-0.525474880170421</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.05516464959188738</v>
+        <v>-0.4555165276644786</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7646046946321903</v>
+        <v>-1.369262363323529</v>
       </c>
     </row>
     <row r="30">
@@ -3462,49 +3462,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.079718425743934</v>
+        <v>-2.957873018916835</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-4.391503321202975</v>
+        <v>-4.392690107647631</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-8.37908907721549</v>
+        <v>-8.379242467219811</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-7.051259143207972</v>
+        <v>-7.051753635585975</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-6.092542708279716</v>
+        <v>-6.043996788513944</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-7.591575864273373</v>
+        <v>-7.56761845532376</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-5.879879037910797</v>
+        <v>-5.831867358920476</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-5.448744088883167</v>
+        <v>-5.39949652648945</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-4.459574297050395</v>
+        <v>-4.538265542811864</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-3.349400470637029</v>
+        <v>-3.565686937998116</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-2.186395153448601</v>
+        <v>-2.572222595115043</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.382082001551034</v>
+        <v>-1.915253462540569</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.7236660316167658</v>
+        <v>-1.412207796290019</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.461567418976408</v>
+        <v>-3.258971317508184</v>
       </c>
     </row>
     <row r="31">
@@ -3514,49 +3514,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-3.069151324651997</v>
+        <v>-2.900736824886984</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-4.680337417715826</v>
+        <v>-4.681524204160482</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-8.604520567176749</v>
+        <v>-8.60467395718107</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-7.689981698098194</v>
+        <v>-7.690476190476197</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-7.836114388448792</v>
+        <v>-7.78756846868302</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-9.499524672539188</v>
+        <v>-9.475567263589575</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-7.231293855334776</v>
+        <v>-7.183282176344456</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-6.521891910886218</v>
+        <v>-6.472644348492501</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-6.785128197407452</v>
+        <v>-6.901773820374395</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-4.281587717648797</v>
+        <v>-4.588347499228597</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-3.883992621438814</v>
+        <v>-4.400331084019577</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-2.84411266676895</v>
+        <v>-3.557850621164491</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-2.250717703349281</v>
+        <v>-3.168694822238123</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-4.824982053122753</v>
+        <v>-5.664747999438447</v>
       </c>
     </row>
     <row r="32">
@@ -3566,49 +3566,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-4.059863398955407</v>
+        <v>-4.089059193308039</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-10.27634719256375</v>
+        <v>-10.27650058256807</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-7.514543101606961</v>
+        <v>-7.515037593984964</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-10.1580958125974</v>
+        <v>-10.10954989283162</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-12.49230073033073</v>
+        <v>-12.46834332138112</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-9.419116352754791</v>
+        <v>-9.371104673764471</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-9.359869207067845</v>
+        <v>-9.310621644674129</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-8.12037795785406</v>
+        <v>-8.294962674863555</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-6.592158737748029</v>
+        <v>-7.013528097783798</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-6.532324681535584</v>
+        <v>-7.217668545319889</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-4.080029215627277</v>
+        <v>-5.054238650060263</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-4.218285270916859</v>
+        <v>-5.449396576624089</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-7.235792863933561</v>
+        <v>-8.358246451450832</v>
       </c>
     </row>
     <row r="33">
@@ -3618,49 +3618,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-6.172191198319588</v>
+        <v>-6.201386992672219</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-7.783377291383417</v>
+        <v>-7.784564077828072</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-11.53385337412503</v>
+        <v>-11.53400676412935</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-8.719064472147409</v>
+        <v>-8.719558964525412</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-10.59963590443773</v>
+        <v>-10.55108998467196</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-14.32910751238654</v>
+        <v>-14.30515010343693</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-9.715831294471499</v>
+        <v>-9.667819615481179</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-10.85404087785555</v>
+        <v>-10.80479331546184</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-7.237352074828181</v>
+        <v>-7.486061226612058</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-4.359563572022161</v>
+        <v>-4.954185109440459</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-4.210150481843257</v>
+        <v>-5.15832555697655</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.3684978845186393</v>
+        <v>-1.744454121625083</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.789606592238172</v>
+        <v>-3.481893927383538</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-2.25831538645609</v>
+        <v>-3.903990004965486</v>
       </c>
     </row>
     <row r="34">
@@ -3670,49 +3670,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-8.730916030534353</v>
+        <v>-8.760111824886984</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-7.663530695026751</v>
+        <v>-7.664717481471406</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-11.62973065121037</v>
+        <v>-11.62988404121469</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-9.713791221907712</v>
+        <v>-9.714285714285715</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-10.25208077500341</v>
+        <v>-10.20353485523763</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-11.74042103108261</v>
+        <v>-11.716463622133</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-6.467988533205919</v>
+        <v>-6.419976854215598</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-8.720771462706942</v>
+        <v>-8.671523900313225</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-6.561676399152496</v>
+        <v>-6.922782223735737</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-3.332971116858289</v>
+        <v>-4.175182233122143</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-2.136504635418724</v>
+        <v>-3.486465537801095</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>1.176840557371527</v>
+        <v>-0.7497273718647719</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>1.293207530295568</v>
+        <v>-1.144885298428598</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.3502156979825699</v>
+        <v>-2.681554722127522</v>
       </c>
     </row>
     <row r="35">
@@ -3722,49 +3722,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-9.623773173391498</v>
+        <v>-9.65296896774413</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-11.23495926645533</v>
+        <v>-11.23614605289998</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-15.20115922263894</v>
+        <v>-15.20131261264326</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-12.68998169809819</v>
+        <v>-12.69047619047619</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-13.22827125119388</v>
+        <v>-13.17972533142811</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-15.31184960251118</v>
+        <v>-15.28789219356157</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-9.444179009396393</v>
+        <v>-9.396167330406072</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-11.10172384365933</v>
+        <v>-11.05247628126561</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-7.017553963463797</v>
+        <v>-7.518020318973839</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-4.840731649009058</v>
+        <v>-5.960896518836435</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-1.943957348070214</v>
+        <v>-3.784084585420139</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>3.769433149964122</v>
+        <v>1.035986913849506</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>1.577130397916534</v>
+        <v>-1.740123393666693</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>1.802866048143066</v>
+        <v>-1.491078531651326</v>
       </c>
     </row>
   </sheetData>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7.042893493275173</v>
+        <v>7.013697698922542</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>16.14599311449705</v>
+        <v>16.14480632805239</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>9.798840777361072</v>
+        <v>9.79868738735675</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.595732587616098</v>
+        <v>1.595238095238095</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>7.009823986901353</v>
+        <v>7.058369906667124</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.73576944510787</v>
+        <v>3.759726854057483</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2.460582895365505</v>
+        <v>2.508594574355826</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-1.577914319849803</v>
+        <v>-1.528666757456087</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>5.503960666484559</v>
+        <v>5.577217776264256</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>8.225470441583283</v>
+        <v>8.324817766877857</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>9.211245473799281</v>
+        <v>9.311153509817956</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>4.48371886424983</v>
+        <v>4.607415485278075</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>10.01594896331737</v>
+        <v>10.1646385110952</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>10.2416846135439</v>
+        <v>10.41368337311057</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>111</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7.879444329826015</v>
+        <v>7.850248535473384</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>17.07906904757299</v>
+        <v>17.07788226112833</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>13.08069405921434</v>
+        <v>13.08054066921002</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>6.003711995595509</v>
+        <v>6.003217503217506</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6.366323343400701</v>
+        <v>6.414869263166473</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4.861895571233994</v>
+        <v>4.885852980183607</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.876284311066925</v>
+        <v>3.924295990057246</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.7065129645774775</v>
+        <v>0.7557605269711942</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>6.050936213460105</v>
+        <v>6.124193323239801</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>9.705521921634769</v>
+        <v>9.804869246929343</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>9.500820763374577</v>
+        <v>9.600728799393252</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>5.931595312126284</v>
+        <v>6.055291933154528</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>10.01594896331737</v>
+        <v>10.1646385110952</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>11.14258551444481</v>
+        <v>11.31458427401147</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>154</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8.558045008426681</v>
+        <v>8.52884921407405</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>15.38841735692129</v>
+        <v>15.38723057047664</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>12.39624337476366</v>
+        <v>12.39608998475934</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7.981013972897479</v>
+        <v>7.980519480519476</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7.442724419801785</v>
+        <v>7.491270339567556</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.142695852034272</v>
+        <v>5.166653260983885</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.40863484341746</v>
+        <v>4.45664652240778</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.993514251578766</v>
+        <v>2.042761813972483</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>7.127337289861188</v>
+        <v>7.200594399640885</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8.874821090933921</v>
+        <v>8.974168416228494</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>9.319470582024394</v>
+        <v>9.419378618043069</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>5.457744838275815</v>
+        <v>5.58144145930406</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>10.2323991797676</v>
+        <v>10.38108872754542</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>9.159433531292841</v>
+        <v>9.331432290859503</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>217</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.96608857776058</v>
+        <v>6.936892783407949</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>11.80651538792256</v>
+        <v>11.8053286014779</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>11.41174400316752</v>
+        <v>11.4115906131632</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>8.776992188230537</v>
+        <v>8.776497695852534</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>6.395384662784608</v>
+        <v>6.443930582550379</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.310270213157018</v>
+        <v>5.334227622106631</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>5.22555985389085</v>
+        <v>5.273571532881171</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.993514251578766</v>
+        <v>2.042761813972483</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>7.46248601210668</v>
+        <v>7.535743121886377</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>9.377544174302173</v>
+        <v>9.476891499596746</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>7.329525043691753</v>
+        <v>7.429433079710428</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>5.520585223696841</v>
+        <v>5.644281844725086</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.943752342733667</v>
+        <v>7.092441890511495</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>7.630317486047751</v>
+        <v>7.802316245614414</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>289</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5.650571858739006</v>
+        <v>5.621376064386375</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>9.921738706851656</v>
+        <v>9.920551920407</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>10.56502960583362</v>
+        <v>10.5648762158293</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>8.273109420702276</v>
+        <v>8.272614928324273</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5.658695300132521</v>
+        <v>5.707241219898293</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.571986284784913</v>
+        <v>4.595943693734526</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.83329668676442</v>
+        <v>4.881308365754741</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.290103475503635</v>
+        <v>2.339351037897352</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6.035349692683276</v>
+        <v>6.108606802462972</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>7.26155546382747</v>
+        <v>7.360902789122044</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>6.018792021830251</v>
+        <v>6.118700057848926</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5.707149412939906</v>
+        <v>5.83084603396815</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>6.325060843363516</v>
+        <v>6.473750391141344</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>6.550796493590049</v>
+        <v>6.722795253156711</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>395</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6.357467807849481</v>
+        <v>6.32827201349685</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>7.680049775135991</v>
+        <v>7.522872706118775</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>9.310594846077159</v>
+        <v>9.149336738006092</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>8.428161761817421</v>
+        <v>8.269119769119769</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>6.117720309987554</v>
+        <v>6.012193860491074</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>5.402436111774534</v>
+        <v>5.274878369208999</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>6.330383980356473</v>
+        <v>6.224323290084541</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.331669766949474</v>
+        <v>3.23323800444868</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>6.81499140789505</v>
+        <v>6.731618930665419</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>7.230895396375324</v>
+        <v>7.170416612476693</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>6.519865124191078</v>
+        <v>6.71375091241535</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>5.288420491736268</v>
+        <v>5.509291387153979</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>5.121434195384886</v>
+        <v>5.270123743162713</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>5.094005288649392</v>
+        <v>5.266004048216054</v>
       </c>
     </row>
     <row r="12">
@@ -4223,46 +4223,46 @@
         <v>501</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.781509416781745</v>
+        <v>3.640681825906668</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5.071244489947638</v>
+        <v>4.835282518528594</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7.189773198233603</v>
+        <v>6.822496911166269</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6.122393551402808</v>
+        <v>5.761904761904752</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.985301603097525</v>
+        <v>4.677417525714745</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.683873237523038</v>
+        <v>4.354964949295578</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>5.197965273466444</v>
+        <v>4.889546955308212</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3.134090242454157</v>
+        <v>3.034825306035984</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>4.869515271560125</v>
+        <v>4.783566982613465</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>5.217201265649429</v>
+        <v>5.150214592274679</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>4.613298510582851</v>
+        <v>4.747661446325878</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3.849273469325396</v>
+        <v>3.932891202403901</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.429122616011988</v>
+        <v>3.458131206978344</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.054059863044913</v>
+        <v>4.226058622611575</v>
       </c>
     </row>
     <row r="13">
@@ -4272,49 +4272,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.221278326832419</v>
+        <v>2.106476594518334</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5.091571345789575</v>
+        <v>4.905146144730246</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.890484982212818</v>
+        <v>5.606869815257483</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.911068170668209</v>
+        <v>3.545830538788287</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.00269987741504</v>
+        <v>3.682559488603182</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.300073907050127</v>
+        <v>3.95534500742211</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>5.002765122587107</v>
+        <v>4.67716153165518</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.960893329194072</v>
+        <v>2.802878067046493</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>4.474714322277592</v>
+        <v>4.33085068482675</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.569677415711517</v>
+        <v>4.445989240161992</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>3.892535312569429</v>
+        <v>3.928859747242498</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3.6119528350035</v>
+        <v>3.610998109550358</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>3.191801981690091</v>
+        <v>3.152602927631058</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>3.417537631916623</v>
+        <v>3.495444379399878</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.461317602328293</v>
+        <v>2.291424666790356</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>4.905327182314416</v>
+        <v>4.805558721199162</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.843885822406108</v>
+        <v>4.539861705995847</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.117578439358851</v>
+        <v>2.877172123650993</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.610216721314707</v>
+        <v>3.412250767590237</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.423054668475565</v>
+        <v>4.19720017885475</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4.982674206116613</v>
+        <v>4.776748955186271</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.840347830371115</v>
+        <v>2.77442451746618</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.325757426425653</v>
+        <v>4.221906420952905</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2.960374712570022</v>
+        <v>2.885257327317412</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.884539533691274</v>
+        <v>2.937527136191576</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.145721809757937</v>
+        <v>2.172975727346667</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.756498791496071</v>
+        <v>2.752470559081502</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.466770524196832</v>
+        <v>2.562975522402724</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.469187919569592</v>
+        <v>1.328062448971934</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.660239187536057</v>
+        <v>3.583059637674999</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.429793158313451</v>
+        <v>3.189321649360295</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.160557057550051</v>
+        <v>1.97065797273266</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.516335568569509</v>
+        <v>2.311284350452937</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.918093731816285</v>
+        <v>2.687804309105886</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3.042151639773508</v>
+        <v>2.834617099548474</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.844394060704929</v>
+        <v>1.746377700160984</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.722869106687369</v>
+        <v>2.599172975789557</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.499255112027654</v>
+        <v>2.398397354476131</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.668249152097317</v>
+        <v>1.675046107355406</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.180706636394184</v>
+        <v>1.169637047499641</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.8649399166924638</v>
+        <v>0.834080065032083</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.195059700530685</v>
+        <v>1.247016706443901</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.080335055477811</v>
+        <v>1.909298920346984</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3.560071789445303</v>
+        <v>3.445705890650409</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.041411957269055</v>
+        <v>2.878657677032407</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.134640833841416</v>
+        <v>2.921886605595446</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.820842378564905</v>
+        <v>2.605947689946817</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.81568807341359</v>
+        <v>3.658629222630559</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3.905345630450817</v>
+        <v>3.771283358708388</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.827989279602185</v>
+        <v>2.785519922415169</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.02855899753451</v>
+        <v>2.972212200746974</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.440192075659752</v>
+        <v>2.372436814496901</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.538019252185961</v>
+        <v>1.560657478071917</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.8749257393276793</v>
+        <v>0.8870481028776851</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.4547748860142704</v>
+        <v>0.4544935835589783</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.029246368847602</v>
+        <v>1.101237768236771</v>
       </c>
     </row>
     <row r="17">
@@ -4480,465 +4480,465 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.050682482476795</v>
+        <v>0.8627569668105721</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.009088352592293</v>
+        <v>1.874094336806685</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.40069164429012</v>
+        <v>2.295775177254022</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.945885167276877</v>
+        <v>2.796304140633261</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.22661316342208</v>
+        <v>2.08466804638261</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.641242081923785</v>
+        <v>2.505711534067366</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.526680976388967</v>
+        <v>3.377606867700464</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.462597407229083</v>
+        <v>2.392486273489226</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.177734653691381</v>
+        <v>2.101239411644478</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.402442723033168</v>
+        <v>1.319935576260143</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.6007266393998449</v>
+        <v>0.5957356933600124</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.1873435977253237</v>
+        <v>0.1756576520332587</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.1403270727701198</v>
+        <v>0.1199956539523512</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.589943320011578</v>
+        <v>0.6345818590872483</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -5.539</t>
+          <t>X &lt; -5.54</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.222787673169357</v>
+        <v>1.145323648730312</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.43505442592258</v>
+        <v>1.342184707248961</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.546374573488215</v>
+        <v>2.474193699226696</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.841048372279289</v>
+        <v>2.794796112977927</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.531438522600396</v>
+        <v>2.43269255371704</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.865600749827067</v>
+        <v>2.805528380775044</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.549628379029826</v>
+        <v>3.481587208710657</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.826313739086771</v>
+        <v>2.797993843089863</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.316901089290454</v>
+        <v>2.288043597988747</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.466982292960594</v>
+        <v>1.437062664837043</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.10917415199701</v>
+        <v>0.1208596513683773</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.3689396879602853</v>
+        <v>-0.3597437922260198</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.2765985489610756</v>
+        <v>-0.2719962066896713</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.3975675945390051</v>
+        <v>0.4605716936561848</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -3.094</t>
+          <t>X &lt; -3.095</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1765</v>
+        <v>1768</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.304394703928921</v>
+        <v>1.232150414842891</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.306428119477005</v>
+        <v>1.224662693783841</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.470140066307408</v>
+        <v>2.406614069565926</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.632598947063101</v>
+        <v>2.592772730926917</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.843453928119068</v>
+        <v>1.765875869097123</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.512917698176793</v>
+        <v>2.464681809012433</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.994779576870968</v>
+        <v>2.943202220231079</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.754339828268371</v>
+        <v>2.735304896594485</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.070128209989214</v>
+        <v>2.054133415616448</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.276866637455399</v>
+        <v>1.262579779131968</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.05233545086658609</v>
+        <v>0.07437579477937106</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.4798586347384273</v>
+        <v>-0.4571527148833354</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.05015113111132052</v>
+        <v>-0.02944477513053556</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.6288423094834741</v>
+        <v>0.7040302811045365</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.6492</t>
+          <t>X &lt; -0.6502</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.7305464200585305</v>
+        <v>0.6656636551721036</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.6286096905392426</v>
+        <v>0.5595914444623347</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.843492465929671</v>
+        <v>1.79066881803832</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.100551041469679</v>
+        <v>2.06826334669762</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.342685844515692</v>
+        <v>1.283593230856468</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.91556142133372</v>
+        <v>1.879595491167493</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.106625653400343</v>
+        <v>2.043904016023077</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.986435106739471</v>
+        <v>1.951186722397395</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.8848186588390874</v>
+        <v>0.8570119830441598</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.03489986250922783</v>
+        <v>0.01146280989011927</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.7148954483773196</v>
+        <v>-0.7082468429157345</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.9778413792727463</v>
+        <v>-0.968530308059016</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.7042360383344146</v>
+        <v>-0.6938225203762087</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.4785003881078822</v>
+        <v>-0.4171771610140453</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 1.796</t>
+          <t>X &lt; 1.794</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2259</v>
+        <v>2263</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.7199669716731592</v>
+        <v>0.6589022596200564</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.3248590071438642</v>
+        <v>0.264105456154347</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.721699182764766</v>
+        <v>1.674944932628371</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.097816710389864</v>
+        <v>2.068913480885314</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.628724178556965</v>
+        <v>1.579664339933395</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.083852040978073</v>
+        <v>2.053430068500461</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.334104681237896</v>
+        <v>2.282036990970049</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.353977161842479</v>
+        <v>2.3260836045662</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.451914881371046</v>
+        <v>1.432596964976788</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.8233329597645209</v>
+        <v>0.8101665601225392</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.1316906771129993</v>
+        <v>0.1456426452779596</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.09953542019967188</v>
+        <v>-0.08038016278246829</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.03274514912175164</v>
+        <v>-0.009095293380646297</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.1044557512154469</v>
+        <v>0.1765350449326348</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 4.241</t>
+          <t>X &lt; 4.239</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2498</v>
+        <v>2502</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.5142916371972746</v>
+        <v>0.456833615176734</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.4824084636970625</v>
+        <v>0.4268225993159902</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.868042558793071</v>
+        <v>1.82519930634178</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.460624725998841</v>
+        <v>2.432980599647259</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.985062082139443</v>
+        <v>1.943731458695339</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.06510117780094</v>
+        <v>2.039939337457213</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.323330236095238</v>
+        <v>2.280843051267524</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.096453746031472</v>
+        <v>2.076938163938316</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.555087282062743</v>
+        <v>1.544224443310817</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.10548874193784</v>
+        <v>1.102152164323975</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.3803712506111978</v>
+        <v>0.4018293010925404</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.02560287885893331</v>
+        <v>0.003353413164887797</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.07466260089411492</v>
+        <v>0.1100373658028957</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.02017407177716279</v>
+        <v>0.1019327735901996</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 6.686</t>
+          <t>X &lt; 6.684</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2696</v>
+        <v>2700</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.2948056571044333</v>
+        <v>0.2399804600890221</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.1840918786232209</v>
+        <v>0.1333629910276741</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.105719084239375</v>
+        <v>1.068528657198016</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.738201579659005</v>
+        <v>1.715208564045767</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.406025758937083</v>
+        <v>1.373615384703292</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.427649311626219</v>
+        <v>1.40866826223079</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.697547710965345</v>
+        <v>1.664222839699647</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.564306960353669</v>
+        <v>1.551789371780536</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.9098529937418718</v>
+        <v>0.9072943540302987</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.6534060075010331</v>
+        <v>0.658925966370667</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.1519689441963337</v>
+        <v>0.1797651053995821</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.2958487491456623</v>
+        <v>-0.2593498737152515</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.2338037567617519</v>
+        <v>-0.1895512951493927</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.3048040115797335</v>
+        <v>-0.2159462565190537</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 9.13</t>
+          <t>X &lt; 9.128</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2925</v>
+        <v>2929</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.402059063290281</v>
+        <v>0.3650157695328815</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.2764985589956765</v>
+        <v>0.2449213655611118</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.16351911711623</v>
+        <v>1.14414016526954</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.688433602448256</v>
+        <v>1.682326350070468</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.442609058565829</v>
+        <v>1.416371786792901</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.212415605964551</v>
+        <v>1.197588617761944</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.557041991824605</v>
+        <v>1.530587567738472</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.363477621542145</v>
+        <v>1.356463444539536</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.9606151231390285</v>
+        <v>0.9638182242143998</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.8970211131339454</v>
+        <v>0.9092023560357063</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.5897558523096578</v>
+        <v>0.6221390227134194</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.145501526032497</v>
+        <v>0.187909709579877</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.03304298041140186</v>
+        <v>0.08500256115209481</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.0831017112424064</v>
+        <v>0.01195354495534673</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 11.58</t>
+          <t>X &lt; 11.57</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3133</v>
+        <v>3136</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.4977395922754582</v>
+        <v>0.4460229494296044</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.2100011268798241</v>
+        <v>0.1660880766068757</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.012010775994888</v>
+        <v>0.98023311435702</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.638249594418816</v>
+        <v>1.618699482335835</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.309208812601973</v>
+        <v>1.27443471096722</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.337343578271017</v>
+        <v>1.310617439299207</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.621587865499109</v>
+        <v>1.585909241870944</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.15451922171237</v>
+        <v>1.13796959791356</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.9658639084707943</v>
+        <v>0.9597165255251952</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.9458206308131309</v>
+        <v>0.9499315066412777</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.5496097374747393</v>
+        <v>0.572777624261434</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.1371318413142646</v>
+        <v>0.171013773541759</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.004245590618154438</v>
+        <v>0.04881660056496884</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.1211199401320115</v>
+        <v>-0.03487104865813961</v>
       </c>
     </row>
     <row r="26">
@@ -4948,101 +4948,101 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3311</v>
+        <v>3315</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.4283393206866322</v>
+        <v>0.3921438142107547</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.371106561564666</v>
+        <v>0.342801315521065</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.078737351375288</v>
+        <v>1.061845282093586</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.135204381161515</v>
+        <v>1.131578947368418</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.9758740350522146</v>
+        <v>0.9598655229641864</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.8070254837552042</v>
+        <v>0.7980456423010338</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.192083952447966</v>
+        <v>1.175490592245218</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.9666341549312349</v>
+        <v>0.9673542344998651</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.6338307963546939</v>
+        <v>0.6460645920990302</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.8409944524561226</v>
+        <v>0.8634481632967379</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.4550791594934296</v>
+        <v>0.4956019727474299</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.09682668665998051</v>
+        <v>0.1487824692136499</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.1297111701028371</v>
+        <v>0.1927848721728154</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.006981449075638579</v>
+        <v>0.09694129166260979</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 16.47</t>
+          <t>X &lt; 16.46</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3475</v>
+        <v>3479</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.2338211139643462</v>
+        <v>0.1984006428688261</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.3619208649075674</v>
+        <v>0.3349140134309394</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.017581794894838</v>
+        <v>1.00165180614232</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.020004884228818</v>
+        <v>1.016889816975798</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.7564857232093303</v>
+        <v>0.7442043321804519</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.5808020496341442</v>
+        <v>0.5740849460181039</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.85729409783211</v>
+        <v>0.8447965250156102</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.7643261734698328</v>
+        <v>0.7679104099962686</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.617013081695255</v>
+        <v>0.632162831209321</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.6879575947179148</v>
+        <v>0.7143834122574475</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.3681485227886583</v>
+        <v>0.4116431025533771</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.2298648046403784</v>
+        <v>0.284971195870277</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.2125916491687008</v>
+        <v>0.2795810398308376</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.2944424073088996</v>
+        <v>0.4012276866106248</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3614</v>
+        <v>3618</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.3643878368689641</v>
+        <v>0.3289179435804854</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.6191440770097216</v>
+        <v>0.5924883777190146</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.9581237276887933</v>
+        <v>0.9429620762841324</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.8825001008143545</v>
+        <v>0.8799023468262632</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.7466550024934264</v>
+        <v>0.7367345527737115</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.8104582417883677</v>
+        <v>0.8042203271223798</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.9624407497413472</v>
+        <v>0.9519443280504163</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.8274141646153694</v>
+        <v>0.8325757527930548</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.7664320080925933</v>
+        <v>0.783439928387601</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.7742885299697093</v>
+        <v>0.8033221448852643</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.5419172001544581</v>
+        <v>0.5872414097666621</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.4102743231793937</v>
+        <v>0.4677154063514877</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.3775058716368846</v>
+        <v>0.4474053896067716</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.3818801494229049</v>
+        <v>0.4634346168916679</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3741</v>
+        <v>3746</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.4006207891027884</v>
+        <v>0.3778306824326876</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.4582047885982377</v>
+        <v>0.4449064586023539</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.6919839395912533</v>
+        <v>0.68997602951044</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.7568362814300613</v>
+        <v>0.7546782291191221</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.607198834276204</v>
+        <v>0.599679906033046</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.7858184254266831</v>
+        <v>0.7806822793815797</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.6624611881043023</v>
+        <v>0.6548394831906705</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.6111489558213279</v>
+        <v>0.603529404590823</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.4967051580261739</v>
+        <v>0.5014284629382928</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.448710980782117</v>
+        <v>0.4657701478302343</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.2440098225219245</v>
+        <v>0.2766808250385111</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.1714646923324707</v>
+        <v>0.2165022363071998</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.1522761485619668</v>
+        <v>0.2100081401317695</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.2176268749713444</v>
+        <v>0.2873263700851254</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3837</v>
+        <v>3842</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.2766281942315203</v>
+        <v>0.2662244491140484</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.5006639445777239</v>
+        <v>0.499342122650468</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.7968328945619234</v>
+        <v>0.7945718558599566</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.7071371077683395</v>
+        <v>0.7051624388072923</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.6258954154727761</v>
+        <v>0.6197206999057414</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.7814410609800575</v>
+        <v>0.7770428713734958</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.659049358553176</v>
+        <v>0.6528249867078344</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.5973342001993416</v>
+        <v>0.5911728623835373</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.5363520436765654</v>
+        <v>0.5426825168784717</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.4422320484934374</v>
+        <v>0.4613603714391772</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.3417790007362385</v>
+        <v>0.3759253223140746</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.2719090425885682</v>
+        <v>0.3187281060600071</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.2166265760356509</v>
+        <v>0.2765302623312209</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.3381141157591898</v>
+        <v>0.4102129583960163</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3915</v>
+        <v>3921</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.2083523864934378</v>
+        <v>0.1977447731297914</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.4209014460091609</v>
+        <v>0.4198054199851313</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.6266179479079312</v>
+        <v>0.6248754414186592</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.5923312270718739</v>
+        <v>0.5907075625976717</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.6039138300343225</v>
+        <v>0.5989006227703584</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.7367903741532942</v>
+        <v>0.7330873359443046</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.6151472485512528</v>
+        <v>0.6101366168347298</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.5452434212854698</v>
+        <v>0.54034266449451</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.5864063107279591</v>
+        <v>0.5939560049230153</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.4259665746636827</v>
+        <v>0.4467467932654756</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.4000192468427031</v>
+        <v>0.4353707808242078</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.3322523532327679</v>
+        <v>0.3805118765238475</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.2951454222891243</v>
+        <v>0.3567173824193617</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.4332554947699663</v>
+        <v>0.4927448370228404</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3980</v>
+        <v>3986</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.2021331169079801</v>
+        <v>0.203066469686668</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.3097037454763125</v>
+        <v>0.308912190507435</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.5557757641003747</v>
+        <v>0.5542540623630003</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.4488723378700215</v>
+        <v>0.447661947661949</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.5769496323402521</v>
+        <v>0.5728820945209847</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.7125038998739583</v>
+        <v>0.7093179073040119</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.5914575455771782</v>
+        <v>0.5873752977646447</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.5653016703895517</v>
+        <v>0.561227316405926</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.5294388306213591</v>
+        <v>0.538201418029665</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.4582188536836114</v>
+        <v>0.4802062380557928</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.4544722294600945</v>
+        <v>0.4907664931411375</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.3381344812879092</v>
+        <v>0.3876132213434218</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.3450120128024352</v>
+        <v>0.407929205853172</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.4594400574300153</v>
+        <v>0.520724684366634</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4021</v>
+        <v>4027</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.2368799486167958</v>
+        <v>0.2374129275882666</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.4014430601158168</v>
+        <v>0.4003976460354011</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.4920189674352144</v>
+        <v>0.4906848401268604</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.4123531255481012</v>
+        <v>0.4112495134293468</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.48394406971709</v>
+        <v>0.4806644934810436</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.6459748791701614</v>
+        <v>0.6432460609967592</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.5004252305098618</v>
+        <v>0.4971206739379568</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.5194785905714525</v>
+        <v>0.5160712964562819</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.4087699298219221</v>
+        <v>0.4184876175341046</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.3047486968933555</v>
+        <v>0.3278655749368227</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.2989535555401801</v>
+        <v>0.3362037284165496</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.1592889431018634</v>
+        <v>0.2098336677409449</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.2115398799426131</v>
+        <v>0.2755289447264531</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.2027224979839417</v>
+        <v>0.2655168306058187</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4058</v>
+        <v>4064</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.2490396999132685</v>
+        <v>0.2492700735677644</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.3236420338433916</v>
+        <v>0.3228052999669799</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.3851737357412688</v>
+        <v>0.3841387458142407</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.3566176947970447</v>
+        <v>0.355670103092784</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.3734028009971482</v>
+        <v>0.3708925587429306</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.4381416030328467</v>
+        <v>0.436216703435349</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.3177257525083732</v>
+        <v>0.3153812536554028</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.3569394442722569</v>
+        <v>0.3544501256607973</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.3205938977519409</v>
+        <v>0.3311060605039842</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.2344100114984542</v>
+        <v>0.2583758508784086</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.2021651232555115</v>
+        <v>0.2401757211121023</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1133602255985124</v>
+        <v>0.1646496922909435</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.112031742326991</v>
+        <v>0.1769386340964374</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.1299711257831078</v>
+        <v>0.1938671001446934</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4086</v>
+        <v>4092</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.2059427872477713</v>
+        <v>0.2060879315076605</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.3422980718574777</v>
+        <v>0.3414089457076557</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.3762740967298654</v>
+        <v>0.3752689827050943</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3488026252131391</v>
+        <v>0.3478790833739538</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.361785798520863</v>
+        <v>0.3596553074404554</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.4281147618112158</v>
+        <v>0.4263935207241545</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.3324028562265653</v>
+        <v>0.33036294991782</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.3436837786506715</v>
+        <v>0.3415835388557085</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.2827016221278953</v>
+        <v>0.2937350885833823</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.2402210445403909</v>
+        <v>0.2646894186635649</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1823268351424403</v>
+        <v>0.2207994194638587</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.06989803863552169</v>
+        <v>0.121757030396374</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1146358567192252</v>
+        <v>0.1801120838617152</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.08505221021547271</v>
+        <v>0.1497537543422496</v>
       </c>
     </row>
   </sheetData>
